--- a/research/traditional_assets/database/data/chile/chile_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_retail_special_lines.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09915159956694841</v>
+        <v>0.09891674024811765</v>
       </c>
       <c r="C2">
-        <v>303.2382687636658</v>
+        <v>301.0988399656275</v>
       </c>
       <c r="D2">
-        <v>269.0382687636658</v>
+        <v>270.2278399656275</v>
       </c>
       <c r="E2">
-        <v>-148.3</v>
+        <v>-144.971</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.329</v>
       </c>
       <c r="G2">
         <v>34.2</v>
@@ -1451,28 +1451,28 @@
         <v>28.25</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1674487</v>
       </c>
       <c r="N2">
-        <v>28.25</v>
+        <v>28.0825513</v>
       </c>
       <c r="O2">
-        <v>7.6275</v>
+        <v>7.582288851</v>
       </c>
       <c r="P2">
-        <v>20.6225</v>
+        <v>20.500262449</v>
       </c>
       <c r="Q2">
-        <v>20.6225</v>
+        <v>20.500262449</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09915159956694841</v>
+        <v>0.09954500025062389</v>
       </c>
       <c r="T2">
-        <v>0.9771532823765235</v>
+        <v>0.9843585540546536</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>168.7083865088233</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09891674024811765</v>
+        <v>0.0986818809292869</v>
       </c>
       <c r="C3">
-        <v>301.0988399656275</v>
+        <v>298.9699774287465</v>
       </c>
       <c r="D3">
-        <v>270.2278399656275</v>
+        <v>271.4279774287465</v>
       </c>
       <c r="E3">
-        <v>-144.971</v>
+        <v>-141.642</v>
       </c>
       <c r="F3">
-        <v>3.329</v>
+        <v>6.657999999999999</v>
       </c>
       <c r="G3">
         <v>34.2</v>
@@ -1533,28 +1533,28 @@
         <v>28.25</v>
       </c>
       <c r="M3">
-        <v>0.1674487</v>
+        <v>0.3348974</v>
       </c>
       <c r="N3">
-        <v>28.0825513</v>
+        <v>27.9151026</v>
       </c>
       <c r="O3">
-        <v>7.582288851</v>
+        <v>7.537077702</v>
       </c>
       <c r="P3">
-        <v>20.500262449</v>
+        <v>20.378024898</v>
       </c>
       <c r="Q3">
-        <v>20.500262449</v>
+        <v>20.378024898</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09954500025062389</v>
+        <v>0.0999464295196805</v>
       </c>
       <c r="T3">
-        <v>0.9843585540546536</v>
+        <v>0.9917108720935616</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>168.7083865088233</v>
+        <v>84.35419325441167</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0986818809292869</v>
+        <v>0.09844702161045613</v>
       </c>
       <c r="C4">
-        <v>298.9699774287465</v>
+        <v>296.8518225618711</v>
       </c>
       <c r="D4">
-        <v>271.4279774287465</v>
+        <v>272.6388225618712</v>
       </c>
       <c r="E4">
-        <v>-141.642</v>
+        <v>-138.313</v>
       </c>
       <c r="F4">
-        <v>6.657999999999999</v>
+        <v>9.986999999999998</v>
       </c>
       <c r="G4">
         <v>34.2</v>
@@ -1615,28 +1615,28 @@
         <v>28.25</v>
       </c>
       <c r="M4">
-        <v>0.3348974</v>
+        <v>0.5023460999999999</v>
       </c>
       <c r="N4">
-        <v>27.9151026</v>
+        <v>27.7476539</v>
       </c>
       <c r="O4">
-        <v>7.537077702</v>
+        <v>7.491866553</v>
       </c>
       <c r="P4">
-        <v>20.378024898</v>
+        <v>20.255787347</v>
       </c>
       <c r="Q4">
-        <v>20.378024898</v>
+        <v>20.255787347</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0999464295196805</v>
+        <v>0.1003561356808826</v>
       </c>
       <c r="T4">
-        <v>0.9917108720935616</v>
+        <v>0.9992147843188389</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>84.35419325441167</v>
+        <v>56.23612883627444</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09844702161045613</v>
+        <v>0.09821216229162537</v>
       </c>
       <c r="C5">
-        <v>296.8518225618711</v>
+        <v>294.7445193084664</v>
       </c>
       <c r="D5">
-        <v>272.6388225618712</v>
+        <v>273.8605193084664</v>
       </c>
       <c r="E5">
-        <v>-138.313</v>
+        <v>-134.984</v>
       </c>
       <c r="F5">
-        <v>9.986999999999998</v>
+        <v>13.316</v>
       </c>
       <c r="G5">
         <v>34.2</v>
@@ -1697,28 +1697,28 @@
         <v>28.25</v>
       </c>
       <c r="M5">
-        <v>0.5023460999999999</v>
+        <v>0.6697947999999999</v>
       </c>
       <c r="N5">
-        <v>27.7476539</v>
+        <v>27.5802052</v>
       </c>
       <c r="O5">
-        <v>7.491866553</v>
+        <v>7.446655404000001</v>
       </c>
       <c r="P5">
-        <v>20.255787347</v>
+        <v>20.133549796</v>
       </c>
       <c r="Q5">
-        <v>20.255787347</v>
+        <v>20.133549796</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1003561356808826</v>
+        <v>0.1007743773871098</v>
       </c>
       <c r="T5">
-        <v>0.9992147843188389</v>
+        <v>1.006875028048809</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.23612883627444</v>
+        <v>42.17709662720583</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09821216229162537</v>
+        <v>0.0979773029727946</v>
       </c>
       <c r="C6">
-        <v>294.7445193084664</v>
+        <v>292.648214203658</v>
       </c>
       <c r="D6">
-        <v>273.8605193084664</v>
+        <v>275.093214203658</v>
       </c>
       <c r="E6">
-        <v>-134.984</v>
+        <v>-131.655</v>
       </c>
       <c r="F6">
-        <v>13.316</v>
+        <v>16.645</v>
       </c>
       <c r="G6">
         <v>34.2</v>
@@ -1779,28 +1779,28 @@
         <v>28.25</v>
       </c>
       <c r="M6">
-        <v>0.6697947999999999</v>
+        <v>0.8372434999999999</v>
       </c>
       <c r="N6">
-        <v>27.5802052</v>
+        <v>27.4127565</v>
       </c>
       <c r="O6">
-        <v>7.446655404000001</v>
+        <v>7.401444255</v>
       </c>
       <c r="P6">
-        <v>20.133549796</v>
+        <v>20.011312245</v>
       </c>
       <c r="Q6">
-        <v>20.133549796</v>
+        <v>20.011312245</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1007743773871098</v>
+        <v>0.1012014241818891</v>
       </c>
       <c r="T6">
-        <v>1.006875028048809</v>
+        <v>1.014696540067832</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.17709662720583</v>
+        <v>33.74167730176466</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0979773029727946</v>
+        <v>0.09774244365396384</v>
       </c>
       <c r="C7">
-        <v>292.648214203658</v>
+        <v>290.5630564328232</v>
       </c>
       <c r="D7">
-        <v>275.093214203658</v>
+        <v>276.3370564328232</v>
       </c>
       <c r="E7">
-        <v>-131.655</v>
+        <v>-128.326</v>
       </c>
       <c r="F7">
-        <v>16.645</v>
+        <v>19.974</v>
       </c>
       <c r="G7">
         <v>34.2</v>
@@ -1861,28 +1861,28 @@
         <v>28.25</v>
       </c>
       <c r="M7">
-        <v>0.8372434999999999</v>
+        <v>1.0046922</v>
       </c>
       <c r="N7">
-        <v>27.4127565</v>
+        <v>27.2453078</v>
       </c>
       <c r="O7">
-        <v>7.401444255</v>
+        <v>7.356233106</v>
       </c>
       <c r="P7">
-        <v>20.011312245</v>
+        <v>19.889074694</v>
       </c>
       <c r="Q7">
-        <v>20.011312245</v>
+        <v>19.889074694</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1012014241818891</v>
+        <v>0.1016375570786849</v>
       </c>
       <c r="T7">
-        <v>1.014696540067832</v>
+        <v>1.022684467236196</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.74167730176466</v>
+        <v>28.11806441813722</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09774244365396384</v>
+        <v>0.0975075843351331</v>
       </c>
       <c r="C8">
-        <v>290.5630564328232</v>
+        <v>288.4891978917795</v>
       </c>
       <c r="D8">
-        <v>276.3370564328232</v>
+        <v>277.5921978917795</v>
       </c>
       <c r="E8">
-        <v>-128.326</v>
+        <v>-124.997</v>
       </c>
       <c r="F8">
-        <v>19.974</v>
+        <v>23.303</v>
       </c>
       <c r="G8">
         <v>34.2</v>
@@ -1943,28 +1943,28 @@
         <v>28.25</v>
       </c>
       <c r="M8">
-        <v>1.0046922</v>
+        <v>1.1721409</v>
       </c>
       <c r="N8">
-        <v>27.2453078</v>
+        <v>27.0778591</v>
       </c>
       <c r="O8">
-        <v>7.356233106</v>
+        <v>7.311021957000001</v>
       </c>
       <c r="P8">
-        <v>19.889074694</v>
+        <v>19.766837143</v>
       </c>
       <c r="Q8">
-        <v>19.889074694</v>
+        <v>19.766837143</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1016375570786849</v>
+        <v>0.1020830691775625</v>
       </c>
       <c r="T8">
-        <v>1.022684467236196</v>
+        <v>1.030844177784524</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.11806441813722</v>
+        <v>24.10119807268905</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09750758433513308</v>
+        <v>0.09727272501630234</v>
       </c>
       <c r="C9">
-        <v>288.4891978917796</v>
+        <v>286.4267932486204</v>
       </c>
       <c r="D9">
-        <v>277.5921978917796</v>
+        <v>278.8587932486204</v>
       </c>
       <c r="E9">
-        <v>-124.997</v>
+        <v>-121.668</v>
       </c>
       <c r="F9">
-        <v>23.303</v>
+        <v>26.632</v>
       </c>
       <c r="G9">
         <v>34.2</v>
@@ -2025,28 +2025,28 @@
         <v>28.25</v>
       </c>
       <c r="M9">
-        <v>1.1721409</v>
+        <v>1.3395896</v>
       </c>
       <c r="N9">
-        <v>27.0778591</v>
+        <v>26.9104104</v>
       </c>
       <c r="O9">
-        <v>7.311021957000001</v>
+        <v>7.265810808</v>
       </c>
       <c r="P9">
-        <v>19.766837143</v>
+        <v>19.644599592</v>
       </c>
       <c r="Q9">
-        <v>19.766837143</v>
+        <v>19.644599592</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1020830691775625</v>
+        <v>0.1025382663220678</v>
       </c>
       <c r="T9">
-        <v>1.030844177784524</v>
+        <v>1.039181273344773</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.10119807268904</v>
+        <v>21.08854831360291</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09727272501630234</v>
+        <v>0.09703786569747157</v>
       </c>
       <c r="C10">
-        <v>286.4267932486204</v>
+        <v>284.3760000072515</v>
       </c>
       <c r="D10">
-        <v>278.8587932486204</v>
+        <v>280.1370000072515</v>
       </c>
       <c r="E10">
-        <v>-121.668</v>
+        <v>-118.339</v>
       </c>
       <c r="F10">
-        <v>26.632</v>
+        <v>29.961</v>
       </c>
       <c r="G10">
         <v>34.2</v>
@@ -2107,28 +2107,28 @@
         <v>28.25</v>
       </c>
       <c r="M10">
-        <v>1.3395896</v>
+        <v>1.5070383</v>
       </c>
       <c r="N10">
-        <v>26.9104104</v>
+        <v>26.7429617</v>
       </c>
       <c r="O10">
-        <v>7.265810808</v>
+        <v>7.220599659</v>
       </c>
       <c r="P10">
-        <v>19.644599592</v>
+        <v>19.522362041</v>
       </c>
       <c r="Q10">
-        <v>19.644599592</v>
+        <v>19.522362041</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1025382663220678</v>
+        <v>0.1030034677994193</v>
       </c>
       <c r="T10">
-        <v>1.039181273344773</v>
+        <v>1.047701601774477</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.08854831360291</v>
+        <v>18.74537627875814</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09703786569747157</v>
+        <v>0.09680300637864081</v>
       </c>
       <c r="C11">
-        <v>284.3760000072515</v>
+        <v>282.3369785726826</v>
       </c>
       <c r="D11">
-        <v>280.1370000072515</v>
+        <v>281.4269785726826</v>
       </c>
       <c r="E11">
-        <v>-118.339</v>
+        <v>-115.01</v>
       </c>
       <c r="F11">
-        <v>29.961</v>
+        <v>33.28999999999999</v>
       </c>
       <c r="G11">
         <v>34.2</v>
@@ -2189,28 +2189,28 @@
         <v>28.25</v>
       </c>
       <c r="M11">
-        <v>1.5070383</v>
+        <v>1.674487</v>
       </c>
       <c r="N11">
-        <v>26.7429617</v>
+        <v>26.575513</v>
       </c>
       <c r="O11">
-        <v>7.220599659</v>
+        <v>7.17538851</v>
       </c>
       <c r="P11">
-        <v>19.522362041</v>
+        <v>19.40012449</v>
       </c>
       <c r="Q11">
-        <v>19.522362041</v>
+        <v>19.40012449</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1030034677994193</v>
+        <v>0.1034790070873787</v>
       </c>
       <c r="T11">
-        <v>1.047701601774477</v>
+        <v>1.056411270835953</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.74537627875814</v>
+        <v>16.87083865088233</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09680300637864081</v>
+        <v>0.09656814705981004</v>
       </c>
       <c r="C12">
-        <v>282.3369785726826</v>
+        <v>280.3098923181324</v>
       </c>
       <c r="D12">
-        <v>281.4269785726826</v>
+        <v>282.7288923181324</v>
       </c>
       <c r="E12">
-        <v>-115.01</v>
+        <v>-111.681</v>
       </c>
       <c r="F12">
-        <v>33.29</v>
+        <v>36.619</v>
       </c>
       <c r="G12">
         <v>34.2</v>
@@ -2271,28 +2271,28 @@
         <v>28.25</v>
       </c>
       <c r="M12">
-        <v>1.674487</v>
+        <v>1.8419357</v>
       </c>
       <c r="N12">
-        <v>26.575513</v>
+        <v>26.4080643</v>
       </c>
       <c r="O12">
-        <v>7.17538851</v>
+        <v>7.130177361</v>
       </c>
       <c r="P12">
-        <v>19.40012449</v>
+        <v>19.277886939</v>
       </c>
       <c r="Q12">
-        <v>19.40012449</v>
+        <v>19.277886939</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1034790070873787</v>
+        <v>0.103965232651472</v>
       </c>
       <c r="T12">
-        <v>1.056411270835953</v>
+        <v>1.065316662797686</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.87083865088233</v>
+        <v>15.33712604625666</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09656814705981004</v>
+        <v>0.0963332877409793</v>
       </c>
       <c r="C13">
-        <v>280.3098923181324</v>
+        <v>278.294907654003</v>
       </c>
       <c r="D13">
-        <v>282.7288923181324</v>
+        <v>284.042907654003</v>
       </c>
       <c r="E13">
-        <v>-111.681</v>
+        <v>-108.352</v>
       </c>
       <c r="F13">
-        <v>36.619</v>
+        <v>39.94799999999999</v>
       </c>
       <c r="G13">
         <v>34.2</v>
@@ -2353,28 +2353,28 @@
         <v>28.25</v>
       </c>
       <c r="M13">
-        <v>1.8419357</v>
+        <v>2.0093844</v>
       </c>
       <c r="N13">
-        <v>26.4080643</v>
+        <v>26.2406156</v>
       </c>
       <c r="O13">
-        <v>7.130177361</v>
+        <v>7.084966212000001</v>
       </c>
       <c r="P13">
-        <v>19.277886939</v>
+        <v>19.155649388</v>
       </c>
       <c r="Q13">
-        <v>19.277886939</v>
+        <v>19.155649388</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.103965232651472</v>
+        <v>0.1044625087965674</v>
       </c>
       <c r="T13">
-        <v>1.065316662797686</v>
+        <v>1.074424450031278</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.33712604625666</v>
+        <v>14.05903220906861</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0963332877409793</v>
+        <v>0.09609842842214852</v>
       </c>
       <c r="C14">
-        <v>278.294907654003</v>
+        <v>276.2921940987889</v>
       </c>
       <c r="D14">
-        <v>284.042907654003</v>
+        <v>285.3691940987889</v>
       </c>
       <c r="E14">
-        <v>-108.352</v>
+        <v>-105.023</v>
       </c>
       <c r="F14">
-        <v>39.94799999999999</v>
+        <v>43.277</v>
       </c>
       <c r="G14">
         <v>34.2</v>
@@ -2435,28 +2435,28 @@
         <v>28.25</v>
       </c>
       <c r="M14">
-        <v>2.0093844</v>
+        <v>2.1768331</v>
       </c>
       <c r="N14">
-        <v>26.2406156</v>
+        <v>26.0731669</v>
       </c>
       <c r="O14">
-        <v>7.084966212000001</v>
+        <v>7.039755063</v>
       </c>
       <c r="P14">
-        <v>19.155649388</v>
+        <v>19.033411837</v>
       </c>
       <c r="Q14">
-        <v>19.155649388</v>
+        <v>19.033411837</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1044625087965674</v>
+        <v>0.1049712165771822</v>
       </c>
       <c r="T14">
-        <v>1.074424450031278</v>
+        <v>1.083741611684032</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.05903220906861</v>
+        <v>12.97756819298641</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09609842842214852</v>
+        <v>0.09601686910331775</v>
       </c>
       <c r="C15">
-        <v>276.2921940987889</v>
+        <v>273.4266741504445</v>
       </c>
       <c r="D15">
-        <v>285.3691940987889</v>
+        <v>285.8326741504445</v>
       </c>
       <c r="E15">
-        <v>-105.023</v>
+        <v>-101.694</v>
       </c>
       <c r="F15">
-        <v>43.277</v>
+        <v>46.606</v>
       </c>
       <c r="G15">
         <v>34.2</v>
@@ -2517,45 +2517,45 @@
         <v>28.25</v>
       </c>
       <c r="M15">
-        <v>2.1768331</v>
+        <v>2.4141908</v>
       </c>
       <c r="N15">
-        <v>26.0731669</v>
+        <v>25.8358092</v>
       </c>
       <c r="O15">
-        <v>7.039755063</v>
+        <v>6.975668484000001</v>
       </c>
       <c r="P15">
-        <v>19.033411837</v>
+        <v>18.860140716</v>
       </c>
       <c r="Q15">
-        <v>19.033411837</v>
+        <v>18.860140716</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1049712165771822</v>
+        <v>0.1054917547712997</v>
       </c>
       <c r="T15">
-        <v>1.083741611684032</v>
+        <v>1.093275451514757</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.27</v>
       </c>
       <c r="W15">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>12.97756819298641</v>
+        <v>11.701643465794</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09601686910331775</v>
+        <v>0.095792959784487</v>
       </c>
       <c r="C16">
-        <v>273.4266741504445</v>
+        <v>271.3778663944023</v>
       </c>
       <c r="D16">
-        <v>285.8326741504445</v>
+        <v>287.1128663944023</v>
       </c>
       <c r="E16">
-        <v>-101.694</v>
+        <v>-98.36500000000001</v>
       </c>
       <c r="F16">
-        <v>46.606</v>
+        <v>49.935</v>
       </c>
       <c r="G16">
         <v>34.2</v>
@@ -2599,28 +2599,28 @@
         <v>28.25</v>
       </c>
       <c r="M16">
-        <v>2.4141908</v>
+        <v>2.586633</v>
       </c>
       <c r="N16">
-        <v>25.8358092</v>
+        <v>25.663367</v>
       </c>
       <c r="O16">
-        <v>6.975668484000001</v>
+        <v>6.929109090000001</v>
       </c>
       <c r="P16">
-        <v>18.860140716</v>
+        <v>18.73425791</v>
       </c>
       <c r="Q16">
-        <v>18.860140716</v>
+        <v>18.73425791</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1054917547712997</v>
+        <v>0.1060245409229259</v>
       </c>
       <c r="T16">
-        <v>1.093275451514757</v>
+        <v>1.103033616988558</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.701643465794</v>
+        <v>10.92153390140774</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.095792959784487</v>
+        <v>0.09556905046565624</v>
       </c>
       <c r="C17">
-        <v>271.3778663944023</v>
+        <v>269.3405777238415</v>
       </c>
       <c r="D17">
-        <v>287.1128663944023</v>
+        <v>288.4045777238415</v>
       </c>
       <c r="E17">
-        <v>-98.36500000000001</v>
+        <v>-95.03600000000002</v>
       </c>
       <c r="F17">
-        <v>49.935</v>
+        <v>53.264</v>
       </c>
       <c r="G17">
         <v>34.2</v>
@@ -2681,28 +2681,28 @@
         <v>28.25</v>
       </c>
       <c r="M17">
-        <v>2.586633</v>
+        <v>2.7590752</v>
       </c>
       <c r="N17">
-        <v>25.663367</v>
+        <v>25.4909248</v>
       </c>
       <c r="O17">
-        <v>6.929109090000001</v>
+        <v>6.882549696000001</v>
       </c>
       <c r="P17">
-        <v>18.73425791</v>
+        <v>18.608375104</v>
       </c>
       <c r="Q17">
-        <v>18.73425791</v>
+        <v>18.608375104</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1060245409229259</v>
+        <v>0.1065700124591146</v>
       </c>
       <c r="T17">
-        <v>1.103033616988558</v>
+        <v>1.113024119735545</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.92153390140774</v>
+        <v>10.23893803256976</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09556905046565624</v>
+        <v>0.09555611114682548</v>
       </c>
       <c r="C18">
-        <v>269.3405777238415</v>
+        <v>266.0865787377352</v>
       </c>
       <c r="D18">
-        <v>288.4045777238415</v>
+        <v>288.4795787377352</v>
       </c>
       <c r="E18">
-        <v>-95.03600000000002</v>
+        <v>-91.70700000000001</v>
       </c>
       <c r="F18">
-        <v>53.264</v>
+        <v>56.593</v>
       </c>
       <c r="G18">
         <v>34.2</v>
@@ -2763,45 +2763,45 @@
         <v>28.25</v>
       </c>
       <c r="M18">
-        <v>2.7590752</v>
+        <v>3.0277255</v>
       </c>
       <c r="N18">
-        <v>25.4909248</v>
+        <v>25.2222745</v>
       </c>
       <c r="O18">
-        <v>6.882549696000001</v>
+        <v>6.810014115</v>
       </c>
       <c r="P18">
-        <v>18.608375104</v>
+        <v>18.412260385</v>
       </c>
       <c r="Q18">
-        <v>18.608375104</v>
+        <v>18.412260385</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1065700124591146</v>
+        <v>0.1071286278877416</v>
       </c>
       <c r="T18">
-        <v>1.113024119735545</v>
+        <v>1.123255357488483</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.27</v>
       </c>
       <c r="W18">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.23893803256976</v>
+        <v>9.33043632918506</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09555611114682548</v>
+        <v>0.09534461182799471</v>
       </c>
       <c r="C19">
-        <v>266.0865787377352</v>
+        <v>263.9890594608345</v>
       </c>
       <c r="D19">
-        <v>288.4795787377352</v>
+        <v>289.7110594608346</v>
       </c>
       <c r="E19">
-        <v>-91.70700000000001</v>
+        <v>-88.37800000000001</v>
       </c>
       <c r="F19">
-        <v>56.593</v>
+        <v>59.922</v>
       </c>
       <c r="G19">
         <v>34.2</v>
@@ -2845,28 +2845,28 @@
         <v>28.25</v>
       </c>
       <c r="M19">
-        <v>3.0277255</v>
+        <v>3.205827</v>
       </c>
       <c r="N19">
-        <v>25.2222745</v>
+        <v>25.044173</v>
       </c>
       <c r="O19">
-        <v>6.810014115</v>
+        <v>6.761926710000001</v>
       </c>
       <c r="P19">
-        <v>18.412260385</v>
+        <v>18.28224629</v>
       </c>
       <c r="Q19">
-        <v>18.412260385</v>
+        <v>18.28224629</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1071286278877416</v>
+        <v>0.1077008680829204</v>
       </c>
       <c r="T19">
-        <v>1.123255357488483</v>
+        <v>1.13373613762564</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.33043632918506</v>
+        <v>8.812078755341446</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09534461182799472</v>
+        <v>0.09513311250916397</v>
       </c>
       <c r="C20">
-        <v>263.9890594608345</v>
+        <v>261.90209931231</v>
       </c>
       <c r="D20">
-        <v>289.7110594608345</v>
+        <v>290.95309931231</v>
       </c>
       <c r="E20">
-        <v>-88.37800000000001</v>
+        <v>-85.04900000000001</v>
       </c>
       <c r="F20">
-        <v>59.922</v>
+        <v>63.251</v>
       </c>
       <c r="G20">
         <v>34.2</v>
@@ -2927,28 +2927,28 @@
         <v>28.25</v>
       </c>
       <c r="M20">
-        <v>3.205827</v>
+        <v>3.3839285</v>
       </c>
       <c r="N20">
-        <v>25.044173</v>
+        <v>24.8660715</v>
       </c>
       <c r="O20">
-        <v>6.761926710000001</v>
+        <v>6.713839305</v>
       </c>
       <c r="P20">
-        <v>18.28224629</v>
+        <v>18.152232195</v>
       </c>
       <c r="Q20">
-        <v>18.28224629</v>
+        <v>18.152232195</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1077008680829204</v>
+        <v>0.1082872376656345</v>
       </c>
       <c r="T20">
-        <v>1.13373613762564</v>
+        <v>1.144475702457541</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.812078755341446</v>
+        <v>8.348285136639266</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09513311250916397</v>
+        <v>0.0949216131903332</v>
       </c>
       <c r="C21">
-        <v>261.90209931231</v>
+        <v>259.82583468315</v>
       </c>
       <c r="D21">
-        <v>290.95309931231</v>
+        <v>292.20583468315</v>
       </c>
       <c r="E21">
-        <v>-85.04900000000001</v>
+        <v>-81.72000000000001</v>
       </c>
       <c r="F21">
-        <v>63.251</v>
+        <v>66.58</v>
       </c>
       <c r="G21">
         <v>34.2</v>
@@ -3009,28 +3009,28 @@
         <v>28.25</v>
       </c>
       <c r="M21">
-        <v>3.3839285</v>
+        <v>3.56203</v>
       </c>
       <c r="N21">
-        <v>24.8660715</v>
+        <v>24.68797</v>
       </c>
       <c r="O21">
-        <v>6.713839305</v>
+        <v>6.6657519</v>
       </c>
       <c r="P21">
-        <v>18.152232195</v>
+        <v>18.0222181</v>
       </c>
       <c r="Q21">
-        <v>18.152232195</v>
+        <v>18.0222181</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1082872376656345</v>
+        <v>0.1088882664879165</v>
       </c>
       <c r="T21">
-        <v>1.144475702457541</v>
+        <v>1.155483756410239</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.348285136639266</v>
+        <v>7.9308708798073</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0949216131903332</v>
+        <v>0.09483275387150243</v>
       </c>
       <c r="C22">
-        <v>259.82583468315</v>
+        <v>257.0263829825657</v>
       </c>
       <c r="D22">
-        <v>292.20583468315</v>
+        <v>292.7353829825657</v>
       </c>
       <c r="E22">
-        <v>-81.72000000000001</v>
+        <v>-78.39100000000001</v>
       </c>
       <c r="F22">
-        <v>66.58</v>
+        <v>69.90900000000001</v>
       </c>
       <c r="G22">
         <v>34.2</v>
@@ -3091,45 +3091,45 @@
         <v>28.25</v>
       </c>
       <c r="M22">
-        <v>3.56203</v>
+        <v>3.796058700000001</v>
       </c>
       <c r="N22">
-        <v>24.68797</v>
+        <v>24.4539413</v>
       </c>
       <c r="O22">
-        <v>6.6657519</v>
+        <v>6.602564151</v>
       </c>
       <c r="P22">
-        <v>18.0222181</v>
+        <v>17.851377149</v>
       </c>
       <c r="Q22">
-        <v>18.0222181</v>
+        <v>17.851377149</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1088882664879165</v>
+        <v>0.1095045112297499</v>
       </c>
       <c r="T22">
-        <v>1.155483756410239</v>
+        <v>1.166770495273133</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.27</v>
       </c>
       <c r="W22">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.9308708798073</v>
+        <v>7.441929177754811</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09483275387150243</v>
+        <v>0.0946270945526717</v>
       </c>
       <c r="C23">
-        <v>257.0263829825657</v>
+        <v>254.9303819970146</v>
       </c>
       <c r="D23">
-        <v>292.7353829825657</v>
+        <v>293.9683819970146</v>
       </c>
       <c r="E23">
-        <v>-78.39100000000002</v>
+        <v>-75.06200000000001</v>
       </c>
       <c r="F23">
-        <v>69.90899999999999</v>
+        <v>73.238</v>
       </c>
       <c r="G23">
         <v>34.2</v>
@@ -3173,28 +3173,28 @@
         <v>28.25</v>
       </c>
       <c r="M23">
-        <v>3.7960587</v>
+        <v>3.9768234</v>
       </c>
       <c r="N23">
-        <v>24.4539413</v>
+        <v>24.2731766</v>
       </c>
       <c r="O23">
-        <v>6.602564151</v>
+        <v>6.553757682000001</v>
       </c>
       <c r="P23">
-        <v>17.851377149</v>
+        <v>17.719418918</v>
       </c>
       <c r="Q23">
-        <v>17.851377149</v>
+        <v>17.719418918</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1095045112297499</v>
+        <v>0.1101365571188098</v>
       </c>
       <c r="T23">
-        <v>1.166770495273133</v>
+        <v>1.178346637696613</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.441929177754813</v>
+        <v>7.103659669675047</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0946270945526717</v>
+        <v>0.0944214352338409</v>
       </c>
       <c r="C24">
-        <v>254.9303819970146</v>
+        <v>252.8448117087977</v>
       </c>
       <c r="D24">
-        <v>293.9683819970146</v>
+        <v>295.2118117087977</v>
       </c>
       <c r="E24">
-        <v>-75.06200000000001</v>
+        <v>-71.73300000000002</v>
       </c>
       <c r="F24">
-        <v>73.238</v>
+        <v>76.56699999999999</v>
       </c>
       <c r="G24">
         <v>34.2</v>
@@ -3255,28 +3255,28 @@
         <v>28.25</v>
       </c>
       <c r="M24">
-        <v>3.9768234</v>
+        <v>4.1575881</v>
       </c>
       <c r="N24">
-        <v>24.2731766</v>
+        <v>24.0924119</v>
       </c>
       <c r="O24">
-        <v>6.553757682000001</v>
+        <v>6.504951213000001</v>
       </c>
       <c r="P24">
-        <v>17.719418918</v>
+        <v>17.587460687</v>
       </c>
       <c r="Q24">
-        <v>17.719418918</v>
+        <v>17.587460687</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1101365571188098</v>
+        <v>0.110785019784209</v>
       </c>
       <c r="T24">
-        <v>1.178346637696613</v>
+        <v>1.19022345914408</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.103659669675047</v>
+        <v>6.794804901428307</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0944214352338409</v>
+        <v>0.09421577591501015</v>
       </c>
       <c r="C25">
-        <v>252.8448117087977</v>
+        <v>250.7698050396781</v>
       </c>
       <c r="D25">
-        <v>295.2118117087977</v>
+        <v>296.4658050396781</v>
       </c>
       <c r="E25">
-        <v>-71.73300000000002</v>
+        <v>-68.40400000000001</v>
       </c>
       <c r="F25">
-        <v>76.56699999999999</v>
+        <v>79.896</v>
       </c>
       <c r="G25">
         <v>34.2</v>
@@ -3337,28 +3337,28 @@
         <v>28.25</v>
       </c>
       <c r="M25">
-        <v>4.1575881</v>
+        <v>4.3383528</v>
       </c>
       <c r="N25">
-        <v>24.0924119</v>
+        <v>23.9116472</v>
       </c>
       <c r="O25">
-        <v>6.504951213000001</v>
+        <v>6.456144744</v>
       </c>
       <c r="P25">
-        <v>17.587460687</v>
+        <v>17.455502456</v>
       </c>
       <c r="Q25">
-        <v>17.587460687</v>
+        <v>17.455502456</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.110785019784209</v>
+        <v>0.1114505472565923</v>
       </c>
       <c r="T25">
-        <v>1.19022345914408</v>
+        <v>1.202412828524375</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.794804901428307</v>
+        <v>6.511688030535461</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09421577591501015</v>
+        <v>0.09401011659617939</v>
       </c>
       <c r="C26">
-        <v>250.7698050396781</v>
+        <v>248.7054971795413</v>
       </c>
       <c r="D26">
-        <v>296.4658050396781</v>
+        <v>297.7304971795413</v>
       </c>
       <c r="E26">
-        <v>-68.40400000000002</v>
+        <v>-65.07500000000002</v>
       </c>
       <c r="F26">
-        <v>79.89599999999999</v>
+        <v>83.22499999999999</v>
       </c>
       <c r="G26">
         <v>34.2</v>
@@ -3419,28 +3419,28 @@
         <v>28.25</v>
       </c>
       <c r="M26">
-        <v>4.338352799999999</v>
+        <v>4.5191175</v>
       </c>
       <c r="N26">
-        <v>23.9116472</v>
+        <v>23.7308825</v>
       </c>
       <c r="O26">
-        <v>6.456144744</v>
+        <v>6.407338275000001</v>
       </c>
       <c r="P26">
-        <v>17.455502456</v>
+        <v>17.323544225</v>
       </c>
       <c r="Q26">
-        <v>17.455502456</v>
+        <v>17.323544225</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1114505472565923</v>
+        <v>0.1121338221282392</v>
       </c>
       <c r="T26">
-        <v>1.202412828524375</v>
+        <v>1.214927247754811</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.511688030535462</v>
+        <v>6.251220509314042</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09401011659617939</v>
+        <v>0.09399425727734861</v>
       </c>
       <c r="C27">
-        <v>248.7054971795413</v>
+        <v>245.4744715679262</v>
       </c>
       <c r="D27">
-        <v>297.7304971795413</v>
+        <v>297.8284715679262</v>
       </c>
       <c r="E27">
-        <v>-65.07500000000002</v>
+        <v>-61.74600000000001</v>
       </c>
       <c r="F27">
-        <v>83.22499999999999</v>
+        <v>86.554</v>
       </c>
       <c r="G27">
         <v>34.2</v>
@@ -3501,45 +3501,45 @@
         <v>28.25</v>
       </c>
       <c r="M27">
-        <v>4.5191175</v>
+        <v>4.786436200000001</v>
       </c>
       <c r="N27">
-        <v>23.7308825</v>
+        <v>23.4635638</v>
       </c>
       <c r="O27">
-        <v>6.407338275000001</v>
+        <v>6.335162226</v>
       </c>
       <c r="P27">
-        <v>17.323544225</v>
+        <v>17.128401574</v>
       </c>
       <c r="Q27">
-        <v>17.323544225</v>
+        <v>17.128401574</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1121338221282392</v>
+        <v>0.112835563888309</v>
       </c>
       <c r="T27">
-        <v>1.214927247754811</v>
+        <v>1.227779894532016</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.27</v>
       </c>
       <c r="W27">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.251220509314042</v>
+        <v>5.90209475684644</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09399425727734861</v>
+        <v>0.09379589795851787</v>
       </c>
       <c r="C28">
-        <v>245.4744715679262</v>
+        <v>243.3763486899603</v>
       </c>
       <c r="D28">
-        <v>297.8284715679262</v>
+        <v>299.0593486899602</v>
       </c>
       <c r="E28">
-        <v>-61.74600000000001</v>
+        <v>-58.41700000000002</v>
       </c>
       <c r="F28">
-        <v>86.554</v>
+        <v>89.883</v>
       </c>
       <c r="G28">
         <v>34.2</v>
@@ -3583,28 +3583,28 @@
         <v>28.25</v>
       </c>
       <c r="M28">
-        <v>4.786436200000001</v>
+        <v>4.9705299</v>
       </c>
       <c r="N28">
-        <v>23.4635638</v>
+        <v>23.2794701</v>
       </c>
       <c r="O28">
-        <v>6.335162226</v>
+        <v>6.285456927000001</v>
       </c>
       <c r="P28">
-        <v>17.128401574</v>
+        <v>16.994013173</v>
       </c>
       <c r="Q28">
-        <v>17.128401574</v>
+        <v>16.994013173</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.112835563888309</v>
+        <v>0.1135565314500245</v>
       </c>
       <c r="T28">
-        <v>1.227779894532016</v>
+        <v>1.240984668618185</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.90209475684644</v>
+        <v>5.683498654741017</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09379589795851787</v>
+        <v>0.09359753863968712</v>
       </c>
       <c r="C29">
-        <v>243.3763486899603</v>
+        <v>241.2884420680793</v>
       </c>
       <c r="D29">
-        <v>299.0593486899602</v>
+        <v>300.3004420680793</v>
       </c>
       <c r="E29">
-        <v>-58.41700000000002</v>
+        <v>-55.08800000000001</v>
       </c>
       <c r="F29">
-        <v>89.883</v>
+        <v>93.212</v>
       </c>
       <c r="G29">
         <v>34.2</v>
@@ -3665,28 +3665,28 @@
         <v>28.25</v>
       </c>
       <c r="M29">
-        <v>4.9705299</v>
+        <v>5.154623600000001</v>
       </c>
       <c r="N29">
-        <v>23.2794701</v>
+        <v>23.0953764</v>
       </c>
       <c r="O29">
-        <v>6.285456927000001</v>
+        <v>6.235751628</v>
       </c>
       <c r="P29">
-        <v>16.994013173</v>
+        <v>16.859624772</v>
       </c>
       <c r="Q29">
-        <v>16.994013173</v>
+        <v>16.859624772</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1135565314500245</v>
+        <v>0.1142975258884543</v>
       </c>
       <c r="T29">
-        <v>1.240984668618185</v>
+        <v>1.254556241984526</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.683498654741017</v>
+        <v>5.480516559928836</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09359753863968712</v>
+        <v>0.09339917932085634</v>
       </c>
       <c r="C30">
-        <v>241.2884420680793</v>
+        <v>239.2108794244185</v>
       </c>
       <c r="D30">
-        <v>300.3004420680793</v>
+        <v>301.5518794244185</v>
       </c>
       <c r="E30">
-        <v>-55.08800000000001</v>
+        <v>-51.759</v>
       </c>
       <c r="F30">
-        <v>93.212</v>
+        <v>96.54100000000001</v>
       </c>
       <c r="G30">
         <v>34.2</v>
@@ -3747,28 +3747,28 @@
         <v>28.25</v>
       </c>
       <c r="M30">
-        <v>5.154623600000001</v>
+        <v>5.338717300000001</v>
       </c>
       <c r="N30">
-        <v>23.0953764</v>
+        <v>22.9112827</v>
       </c>
       <c r="O30">
-        <v>6.235751628</v>
+        <v>6.186046329000001</v>
       </c>
       <c r="P30">
-        <v>16.859624772</v>
+        <v>16.725236371</v>
       </c>
       <c r="Q30">
-        <v>16.859624772</v>
+        <v>16.725236371</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1142975258884543</v>
+        <v>0.1150593934096568</v>
       </c>
       <c r="T30">
-        <v>1.254556241984526</v>
+        <v>1.268510113192171</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.480516559928836</v>
+        <v>5.291533230276118</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09339917932085634</v>
+        <v>0.09320082000202559</v>
       </c>
       <c r="C31">
-        <v>239.2108794244185</v>
+        <v>237.1437906190392</v>
       </c>
       <c r="D31">
-        <v>301.5518794244185</v>
+        <v>302.8137906190392</v>
       </c>
       <c r="E31">
-        <v>-51.75900000000003</v>
+        <v>-48.43000000000002</v>
       </c>
       <c r="F31">
-        <v>96.54099999999998</v>
+        <v>99.86999999999999</v>
       </c>
       <c r="G31">
         <v>34.2</v>
@@ -3829,28 +3829,28 @@
         <v>28.25</v>
       </c>
       <c r="M31">
-        <v>5.338717299999999</v>
+        <v>5.522811</v>
       </c>
       <c r="N31">
-        <v>22.9112827</v>
+        <v>22.727189</v>
       </c>
       <c r="O31">
-        <v>6.186046329000001</v>
+        <v>6.136341030000001</v>
       </c>
       <c r="P31">
-        <v>16.725236371</v>
+        <v>16.59084797</v>
       </c>
       <c r="Q31">
-        <v>16.725236371</v>
+        <v>16.59084797</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1150593934096568</v>
+        <v>0.1158430285743223</v>
       </c>
       <c r="T31">
-        <v>1.268510113192171</v>
+        <v>1.282862666434322</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.29153323027612</v>
+        <v>5.115148789266915</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09320082000202559</v>
+        <v>0.09300246068319483</v>
       </c>
       <c r="C32">
-        <v>237.1437906190392</v>
+        <v>235.0873076948521</v>
       </c>
       <c r="D32">
-        <v>302.8137906190392</v>
+        <v>304.0863076948522</v>
       </c>
       <c r="E32">
-        <v>-48.43000000000002</v>
+        <v>-45.10100000000001</v>
       </c>
       <c r="F32">
-        <v>99.86999999999999</v>
+        <v>103.199</v>
       </c>
       <c r="G32">
         <v>34.2</v>
@@ -3911,28 +3911,28 @@
         <v>28.25</v>
       </c>
       <c r="M32">
-        <v>5.522811</v>
+        <v>5.7069047</v>
       </c>
       <c r="N32">
-        <v>22.727189</v>
+        <v>22.5430953</v>
       </c>
       <c r="O32">
-        <v>6.136341030000001</v>
+        <v>6.086635731</v>
       </c>
       <c r="P32">
-        <v>16.59084797</v>
+        <v>16.456459569</v>
       </c>
       <c r="Q32">
-        <v>16.59084797</v>
+        <v>16.456459569</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1158430285743223</v>
+        <v>0.1166493778017317</v>
       </c>
       <c r="T32">
-        <v>1.282862666434322</v>
+        <v>1.297631235712476</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.115148789266915</v>
+        <v>4.950143989613144</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09300246068319483</v>
+        <v>0.09280410136436405</v>
       </c>
       <c r="C33">
-        <v>235.0873076948521</v>
+        <v>233.0415649236745</v>
       </c>
       <c r="D33">
-        <v>304.0863076948522</v>
+        <v>305.3695649236745</v>
       </c>
       <c r="E33">
-        <v>-45.10100000000001</v>
+        <v>-41.77200000000002</v>
       </c>
       <c r="F33">
-        <v>103.199</v>
+        <v>106.528</v>
       </c>
       <c r="G33">
         <v>34.2</v>
@@ -3993,28 +3993,28 @@
         <v>28.25</v>
       </c>
       <c r="M33">
-        <v>5.7069047</v>
+        <v>5.8909984</v>
       </c>
       <c r="N33">
-        <v>22.5430953</v>
+        <v>22.3590016</v>
       </c>
       <c r="O33">
-        <v>6.086635731</v>
+        <v>6.036930432</v>
       </c>
       <c r="P33">
-        <v>16.456459569</v>
+        <v>16.322071168</v>
       </c>
       <c r="Q33">
-        <v>16.456459569</v>
+        <v>16.322071168</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1166493778017317</v>
+        <v>0.1174794431828883</v>
       </c>
       <c r="T33">
-        <v>1.297631235712476</v>
+        <v>1.312834174675282</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.950143989613144</v>
+        <v>4.795451989937733</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09280410136436405</v>
+        <v>0.0926057420455333</v>
       </c>
       <c r="C34">
-        <v>233.0415649236745</v>
+        <v>231.0066988534597</v>
       </c>
       <c r="D34">
-        <v>305.3695649236745</v>
+        <v>306.6636988534597</v>
       </c>
       <c r="E34">
-        <v>-41.77200000000002</v>
+        <v>-38.44300000000001</v>
       </c>
       <c r="F34">
-        <v>106.528</v>
+        <v>109.857</v>
       </c>
       <c r="G34">
         <v>34.2</v>
@@ -4075,28 +4075,28 @@
         <v>28.25</v>
       </c>
       <c r="M34">
-        <v>5.8909984</v>
+        <v>6.0750921</v>
       </c>
       <c r="N34">
-        <v>22.3590016</v>
+        <v>22.1749079</v>
       </c>
       <c r="O34">
-        <v>6.036930432</v>
+        <v>5.987225133000001</v>
       </c>
       <c r="P34">
-        <v>16.322071168</v>
+        <v>16.187682767</v>
       </c>
       <c r="Q34">
-        <v>16.322071168</v>
+        <v>16.187682767</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1174794431828883</v>
+        <v>0.1183342866351244</v>
       </c>
       <c r="T34">
-        <v>1.312834174675282</v>
+        <v>1.328490932711605</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.795451989937733</v>
+        <v>4.650135262969923</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0926057420455333</v>
+        <v>0.09240738272670254</v>
       </c>
       <c r="C35">
-        <v>231.0066988534597</v>
+        <v>228.9828483567345</v>
       </c>
       <c r="D35">
-        <v>306.6636988534597</v>
+        <v>307.9688483567346</v>
       </c>
       <c r="E35">
-        <v>-38.44300000000001</v>
+        <v>-35.114</v>
       </c>
       <c r="F35">
-        <v>109.857</v>
+        <v>113.186</v>
       </c>
       <c r="G35">
         <v>34.2</v>
@@ -4157,28 +4157,28 @@
         <v>28.25</v>
       </c>
       <c r="M35">
-        <v>6.0750921</v>
+        <v>6.259185800000001</v>
       </c>
       <c r="N35">
-        <v>22.1749079</v>
+        <v>21.9908142</v>
       </c>
       <c r="O35">
-        <v>5.987225133000001</v>
+        <v>5.937519834</v>
       </c>
       <c r="P35">
-        <v>16.187682767</v>
+        <v>16.053294366</v>
       </c>
       <c r="Q35">
-        <v>16.187682767</v>
+        <v>16.053294366</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1183342866351244</v>
+        <v>0.1192150344343978</v>
       </c>
       <c r="T35">
-        <v>1.328490932711605</v>
+        <v>1.344622137961149</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.650135262969923</v>
+        <v>4.513366578764924</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09240738272670254</v>
+        <v>0.09284777340787177</v>
       </c>
       <c r="C36">
-        <v>228.9828483567345</v>
+        <v>222.7711059635731</v>
       </c>
       <c r="D36">
-        <v>307.9688483567346</v>
+        <v>305.0861059635731</v>
       </c>
       <c r="E36">
-        <v>-35.114</v>
+        <v>-31.78500000000001</v>
       </c>
       <c r="F36">
-        <v>113.186</v>
+        <v>116.515</v>
       </c>
       <c r="G36">
         <v>34.2</v>
@@ -4239,45 +4239,45 @@
         <v>28.25</v>
       </c>
       <c r="M36">
-        <v>6.259185800000001</v>
+        <v>6.734567</v>
       </c>
       <c r="N36">
-        <v>21.9908142</v>
+        <v>21.515433</v>
       </c>
       <c r="O36">
-        <v>5.937519834</v>
+        <v>5.809166910000001</v>
       </c>
       <c r="P36">
-        <v>16.053294366</v>
+        <v>15.70626609</v>
       </c>
       <c r="Q36">
-        <v>16.053294366</v>
+        <v>15.70626609</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1192150344343978</v>
+        <v>0.1201228821659566</v>
       </c>
       <c r="T36">
-        <v>1.344622137961149</v>
+        <v>1.361249687987603</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.27</v>
       </c>
       <c r="W36">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.513366578764924</v>
+        <v>4.19477599673446</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09284777340787177</v>
+        <v>0.09266766408904101</v>
       </c>
       <c r="C37">
-        <v>222.7711059635731</v>
+        <v>220.6145315964238</v>
       </c>
       <c r="D37">
-        <v>305.0861059635731</v>
+        <v>306.2585315964238</v>
       </c>
       <c r="E37">
-        <v>-31.78500000000001</v>
+        <v>-28.456</v>
       </c>
       <c r="F37">
-        <v>116.515</v>
+        <v>119.844</v>
       </c>
       <c r="G37">
         <v>34.2</v>
@@ -4321,28 +4321,28 @@
         <v>28.25</v>
       </c>
       <c r="M37">
-        <v>6.734567</v>
+        <v>6.926983200000001</v>
       </c>
       <c r="N37">
-        <v>21.515433</v>
+        <v>21.3230168</v>
       </c>
       <c r="O37">
-        <v>5.809166910000001</v>
+        <v>5.757214536</v>
       </c>
       <c r="P37">
-        <v>15.70626609</v>
+        <v>15.565802264</v>
       </c>
       <c r="Q37">
-        <v>15.70626609</v>
+        <v>15.565802264</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1201228821659566</v>
+        <v>0.1210591001391266</v>
       </c>
       <c r="T37">
-        <v>1.361249687987603</v>
+        <v>1.378396848952383</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.19477599673446</v>
+        <v>4.078254441269612</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09266766408904102</v>
+        <v>0.09343290477021027</v>
       </c>
       <c r="C38">
-        <v>220.6145315964238</v>
+        <v>212.3653721296992</v>
       </c>
       <c r="D38">
-        <v>306.2585315964238</v>
+        <v>301.3383721296992</v>
       </c>
       <c r="E38">
-        <v>-28.45600000000002</v>
+        <v>-25.12700000000002</v>
       </c>
       <c r="F38">
-        <v>119.844</v>
+        <v>123.173</v>
       </c>
       <c r="G38">
         <v>34.2</v>
@@ -4403,45 +4403,45 @@
         <v>28.25</v>
       </c>
       <c r="M38">
-        <v>6.9269832</v>
+        <v>7.550504899999999</v>
       </c>
       <c r="N38">
-        <v>21.3230168</v>
+        <v>20.6994951</v>
       </c>
       <c r="O38">
-        <v>5.757214536</v>
+        <v>5.588863677</v>
       </c>
       <c r="P38">
-        <v>15.565802264</v>
+        <v>15.110631423</v>
       </c>
       <c r="Q38">
-        <v>15.565802264</v>
+        <v>15.110631423</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1210591001391266</v>
+        <v>0.1220250393177941</v>
       </c>
       <c r="T38">
-        <v>1.378396848952383</v>
+        <v>1.396088364233506</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.27</v>
       </c>
       <c r="W38">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.078254441269613</v>
+        <v>3.741471646485522</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09343290477021027</v>
+        <v>0.0932783454513795</v>
       </c>
       <c r="C39">
-        <v>212.3653721296992</v>
+        <v>210.0173383594856</v>
       </c>
       <c r="D39">
-        <v>301.3383721296992</v>
+        <v>302.3193383594856</v>
       </c>
       <c r="E39">
-        <v>-25.12700000000002</v>
+        <v>-21.79800000000002</v>
       </c>
       <c r="F39">
-        <v>123.173</v>
+        <v>126.502</v>
       </c>
       <c r="G39">
         <v>34.2</v>
@@ -4485,28 +4485,28 @@
         <v>28.25</v>
       </c>
       <c r="M39">
-        <v>7.550504899999999</v>
+        <v>7.754572599999999</v>
       </c>
       <c r="N39">
-        <v>20.6994951</v>
+        <v>20.4954274</v>
       </c>
       <c r="O39">
-        <v>5.588863677</v>
+        <v>5.533765398000001</v>
       </c>
       <c r="P39">
-        <v>15.110631423</v>
+        <v>14.961662002</v>
       </c>
       <c r="Q39">
-        <v>15.110631423</v>
+        <v>14.961662002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1220250393177941</v>
+        <v>0.1230221378248056</v>
       </c>
       <c r="T39">
-        <v>1.396088364233506</v>
+        <v>1.414350573555955</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.741471646485522</v>
+        <v>3.643011866314851</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0932783454513795</v>
+        <v>0.09312378613254874</v>
       </c>
       <c r="C40">
-        <v>210.0173383594856</v>
+        <v>207.6757122537749</v>
       </c>
       <c r="D40">
-        <v>302.3193383594856</v>
+        <v>303.3067122537749</v>
       </c>
       <c r="E40">
-        <v>-21.79800000000002</v>
+        <v>-18.46900000000002</v>
       </c>
       <c r="F40">
-        <v>126.502</v>
+        <v>129.831</v>
       </c>
       <c r="G40">
         <v>34.2</v>
@@ -4567,28 +4567,28 @@
         <v>28.25</v>
       </c>
       <c r="M40">
-        <v>7.754572599999999</v>
+        <v>7.958640299999999</v>
       </c>
       <c r="N40">
-        <v>20.4954274</v>
+        <v>20.2913597</v>
       </c>
       <c r="O40">
-        <v>5.533765398000001</v>
+        <v>5.478667119000001</v>
       </c>
       <c r="P40">
-        <v>14.961662002</v>
+        <v>14.812692581</v>
       </c>
       <c r="Q40">
-        <v>14.961662002</v>
+        <v>14.812692581</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1230221378248056</v>
+        <v>0.1240519280861455</v>
       </c>
       <c r="T40">
-        <v>1.414350573555955</v>
+        <v>1.433211543839796</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.643011866314851</v>
+        <v>3.549601305640111</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09312378613254874</v>
+        <v>0.09378682681371799</v>
       </c>
       <c r="C41">
-        <v>207.6757122537749</v>
+        <v>200.155881093452</v>
       </c>
       <c r="D41">
-        <v>303.3067122537749</v>
+        <v>299.115881093452</v>
       </c>
       <c r="E41">
-        <v>-18.46900000000002</v>
+        <v>-15.14000000000001</v>
       </c>
       <c r="F41">
-        <v>129.831</v>
+        <v>133.16</v>
       </c>
       <c r="G41">
         <v>34.2</v>
@@ -4649,45 +4649,45 @@
         <v>28.25</v>
       </c>
       <c r="M41">
-        <v>7.958640299999999</v>
+        <v>8.535556</v>
       </c>
       <c r="N41">
-        <v>20.2913597</v>
+        <v>19.714444</v>
       </c>
       <c r="O41">
-        <v>5.478667119000001</v>
+        <v>5.32289988</v>
       </c>
       <c r="P41">
-        <v>14.812692581</v>
+        <v>14.39154412</v>
       </c>
       <c r="Q41">
-        <v>14.812692581</v>
+        <v>14.39154412</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1240519280861455</v>
+        <v>0.12511604468953</v>
       </c>
       <c r="T41">
-        <v>1.433211543839796</v>
+        <v>1.452701213133099</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.549601305640111</v>
+        <v>3.309684805535808</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09378682681371799</v>
+        <v>0.09365270749488722</v>
       </c>
       <c r="C42">
-        <v>200.155881093452</v>
+        <v>197.6652290224173</v>
       </c>
       <c r="D42">
-        <v>299.115881093452</v>
+        <v>299.9542290224173</v>
       </c>
       <c r="E42">
-        <v>-15.14000000000001</v>
+        <v>-11.81100000000001</v>
       </c>
       <c r="F42">
-        <v>133.16</v>
+        <v>136.489</v>
       </c>
       <c r="G42">
         <v>34.2</v>
@@ -4731,28 +4731,28 @@
         <v>28.25</v>
       </c>
       <c r="M42">
-        <v>8.535556</v>
+        <v>8.748944900000001</v>
       </c>
       <c r="N42">
-        <v>19.714444</v>
+        <v>19.5010551</v>
       </c>
       <c r="O42">
-        <v>5.32289988</v>
+        <v>5.265284877</v>
       </c>
       <c r="P42">
-        <v>14.39154412</v>
+        <v>14.235770223</v>
       </c>
       <c r="Q42">
-        <v>14.39154412</v>
+        <v>14.235770223</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.12511604468953</v>
+        <v>0.1262162330421817</v>
       </c>
       <c r="T42">
-        <v>1.452701213133099</v>
+        <v>1.472851549182106</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.309684805535808</v>
+        <v>3.228960785888593</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09365270749488722</v>
+        <v>0.09351858817605647</v>
       </c>
       <c r="C43">
-        <v>197.6652290224173</v>
+        <v>195.1792895238818</v>
       </c>
       <c r="D43">
-        <v>299.9542290224173</v>
+        <v>300.7972895238818</v>
       </c>
       <c r="E43">
-        <v>-11.81100000000001</v>
+        <v>-8.481999999999999</v>
       </c>
       <c r="F43">
-        <v>136.489</v>
+        <v>139.818</v>
       </c>
       <c r="G43">
         <v>34.2</v>
@@ -4813,28 +4813,28 @@
         <v>28.25</v>
       </c>
       <c r="M43">
-        <v>8.748944900000001</v>
+        <v>8.962333800000001</v>
       </c>
       <c r="N43">
-        <v>19.5010551</v>
+        <v>19.2876662</v>
       </c>
       <c r="O43">
-        <v>5.265284877</v>
+        <v>5.207669874</v>
       </c>
       <c r="P43">
-        <v>14.235770223</v>
+        <v>14.079996326</v>
       </c>
       <c r="Q43">
-        <v>14.235770223</v>
+        <v>14.079996326</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1262162330421817</v>
+        <v>0.1273543589242353</v>
       </c>
       <c r="T43">
-        <v>1.472851549182106</v>
+        <v>1.493696724405217</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.228960785888593</v>
+        <v>3.15208076717696</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09351858817605646</v>
+        <v>0.09338446885722572</v>
       </c>
       <c r="C44">
-        <v>195.1792895238819</v>
+        <v>192.6981024457435</v>
       </c>
       <c r="D44">
-        <v>300.7972895238819</v>
+        <v>301.6451024457435</v>
       </c>
       <c r="E44">
-        <v>-8.482000000000028</v>
+        <v>-5.15300000000002</v>
       </c>
       <c r="F44">
-        <v>139.818</v>
+        <v>143.147</v>
       </c>
       <c r="G44">
         <v>34.2</v>
@@ -4895,28 +4895,28 @@
         <v>28.25</v>
       </c>
       <c r="M44">
-        <v>8.9623338</v>
+        <v>9.1757227</v>
       </c>
       <c r="N44">
-        <v>19.2876662</v>
+        <v>19.0742773</v>
       </c>
       <c r="O44">
-        <v>5.207669874</v>
+        <v>5.150054871</v>
       </c>
       <c r="P44">
-        <v>14.079996326</v>
+        <v>13.924222429</v>
       </c>
       <c r="Q44">
-        <v>14.079996326</v>
+        <v>13.924222429</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1273543589242353</v>
+        <v>0.1285324190477644</v>
       </c>
       <c r="T44">
-        <v>1.493696724405217</v>
+        <v>1.515273309285279</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.15208076717696</v>
+        <v>3.078776563289124</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09338446885722572</v>
+        <v>0.09325034953839494</v>
       </c>
       <c r="C45">
-        <v>192.6981024457435</v>
+        <v>190.2217080864233</v>
       </c>
       <c r="D45">
-        <v>301.6451024457435</v>
+        <v>302.4977080864234</v>
       </c>
       <c r="E45">
-        <v>-5.15300000000002</v>
+        <v>-1.824000000000012</v>
       </c>
       <c r="F45">
-        <v>143.147</v>
+        <v>146.476</v>
       </c>
       <c r="G45">
         <v>34.2</v>
@@ -4977,28 +4977,28 @@
         <v>28.25</v>
       </c>
       <c r="M45">
-        <v>9.1757227</v>
+        <v>9.3891116</v>
       </c>
       <c r="N45">
-        <v>19.0742773</v>
+        <v>18.8608884</v>
       </c>
       <c r="O45">
-        <v>5.150054871</v>
+        <v>5.092439868</v>
       </c>
       <c r="P45">
-        <v>13.924222429</v>
+        <v>13.768448532</v>
       </c>
       <c r="Q45">
-        <v>13.924222429</v>
+        <v>13.768448532</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1285324190477644</v>
+        <v>0.1297525527471338</v>
       </c>
       <c r="T45">
-        <v>1.515273309285279</v>
+        <v>1.537620486482487</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.078776563289124</v>
+        <v>3.008804368668917</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09325034953839494</v>
+        <v>0.09567853021956418</v>
       </c>
       <c r="C46">
-        <v>190.2217080864233</v>
+        <v>172.1665506066401</v>
       </c>
       <c r="D46">
-        <v>302.4977080864234</v>
+        <v>287.7715506066401</v>
       </c>
       <c r="E46">
-        <v>-1.824000000000012</v>
+        <v>1.504999999999995</v>
       </c>
       <c r="F46">
-        <v>146.476</v>
+        <v>149.805</v>
       </c>
       <c r="G46">
         <v>34.2</v>
@@ -5059,45 +5059,45 @@
         <v>28.25</v>
       </c>
       <c r="M46">
-        <v>9.3891116</v>
+        <v>10.7709795</v>
       </c>
       <c r="N46">
-        <v>18.8608884</v>
+        <v>17.4790205</v>
       </c>
       <c r="O46">
-        <v>5.092439868</v>
+        <v>4.719335535</v>
       </c>
       <c r="P46">
-        <v>13.768448532</v>
+        <v>12.759684965</v>
       </c>
       <c r="Q46">
-        <v>13.768448532</v>
+        <v>12.759684965</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1297525527471338</v>
+        <v>0.1310170549446621</v>
       </c>
       <c r="T46">
-        <v>1.537620486482487</v>
+        <v>1.560780288305047</v>
       </c>
       <c r="U46">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.008804368668917</v>
+        <v>2.622788391714978</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09567853021956418</v>
+        <v>0.09560135090073342</v>
       </c>
       <c r="C47">
-        <v>172.1665506066401</v>
+        <v>169.2835226907903</v>
       </c>
       <c r="D47">
-        <v>287.7715506066401</v>
+        <v>288.2175226907903</v>
       </c>
       <c r="E47">
-        <v>1.504999999999995</v>
+        <v>4.833999999999975</v>
       </c>
       <c r="F47">
-        <v>149.805</v>
+        <v>153.134</v>
       </c>
       <c r="G47">
         <v>34.2</v>
@@ -5141,28 +5141,28 @@
         <v>28.25</v>
       </c>
       <c r="M47">
-        <v>10.7709795</v>
+        <v>11.0103346</v>
       </c>
       <c r="N47">
-        <v>17.4790205</v>
+        <v>17.2396654</v>
       </c>
       <c r="O47">
-        <v>4.719335535</v>
+        <v>4.654709658000001</v>
       </c>
       <c r="P47">
-        <v>12.759684965</v>
+        <v>12.584955742</v>
       </c>
       <c r="Q47">
-        <v>12.759684965</v>
+        <v>12.584955742</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1310170549446621</v>
+        <v>0.1323283905569137</v>
       </c>
       <c r="T47">
-        <v>1.560780288305047</v>
+        <v>1.58479786056548</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.622788391714978</v>
+        <v>2.565771252764653</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09560135090073342</v>
+        <v>0.09552417158190266</v>
       </c>
       <c r="C48">
-        <v>169.2835226907903</v>
+        <v>166.401879205111</v>
       </c>
       <c r="D48">
-        <v>288.2175226907903</v>
+        <v>288.664879205111</v>
       </c>
       <c r="E48">
-        <v>4.833999999999975</v>
+        <v>8.162999999999982</v>
       </c>
       <c r="F48">
-        <v>153.134</v>
+        <v>156.463</v>
       </c>
       <c r="G48">
         <v>34.2</v>
@@ -5223,28 +5223,28 @@
         <v>28.25</v>
       </c>
       <c r="M48">
-        <v>11.0103346</v>
+        <v>11.2496897</v>
       </c>
       <c r="N48">
-        <v>17.2396654</v>
+        <v>17.0003103</v>
       </c>
       <c r="O48">
-        <v>4.654709658000001</v>
+        <v>4.590083781</v>
       </c>
       <c r="P48">
-        <v>12.584955742</v>
+        <v>12.410226519</v>
       </c>
       <c r="Q48">
-        <v>12.584955742</v>
+        <v>12.410226519</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1323283905569137</v>
+        <v>0.1336892105318918</v>
       </c>
       <c r="T48">
-        <v>1.58479786056548</v>
+        <v>1.609721756307439</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.565771252764653</v>
+        <v>2.511180375046256</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09552417158190266</v>
+        <v>0.09681355226307189</v>
       </c>
       <c r="C49">
-        <v>166.401879205111</v>
+        <v>155.7767999856179</v>
       </c>
       <c r="D49">
-        <v>288.664879205111</v>
+        <v>281.368799985618</v>
       </c>
       <c r="E49">
-        <v>8.162999999999982</v>
+        <v>11.49199999999999</v>
       </c>
       <c r="F49">
-        <v>156.463</v>
+        <v>159.792</v>
       </c>
       <c r="G49">
         <v>34.2</v>
@@ -5305,45 +5305,45 @@
         <v>28.25</v>
       </c>
       <c r="M49">
-        <v>11.2496897</v>
+        <v>12.1122336</v>
       </c>
       <c r="N49">
-        <v>17.0003103</v>
+        <v>16.1377664</v>
       </c>
       <c r="O49">
-        <v>4.590083781</v>
+        <v>4.357196928</v>
       </c>
       <c r="P49">
-        <v>12.410226519</v>
+        <v>11.780569472</v>
       </c>
       <c r="Q49">
-        <v>12.410226519</v>
+        <v>11.780569472</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1336892105318918</v>
+        <v>0.1351023697366767</v>
       </c>
       <c r="T49">
-        <v>1.609721756307439</v>
+        <v>1.635604263424089</v>
       </c>
       <c r="U49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.27</v>
       </c>
       <c r="W49">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.511180375046256</v>
+        <v>2.332352638905511</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09681355226307189</v>
+        <v>0.09676484294424113</v>
       </c>
       <c r="C50">
-        <v>155.776799985618</v>
+        <v>152.716716395358</v>
       </c>
       <c r="D50">
-        <v>281.368799985618</v>
+        <v>281.637716395358</v>
       </c>
       <c r="E50">
-        <v>11.49199999999996</v>
+        <v>14.82099999999997</v>
       </c>
       <c r="F50">
-        <v>159.792</v>
+        <v>163.121</v>
       </c>
       <c r="G50">
         <v>34.2</v>
@@ -5387,28 +5387,28 @@
         <v>28.25</v>
       </c>
       <c r="M50">
-        <v>12.1122336</v>
+        <v>12.3645718</v>
       </c>
       <c r="N50">
-        <v>16.1377664</v>
+        <v>15.8854282</v>
       </c>
       <c r="O50">
-        <v>4.357196928</v>
+        <v>4.289065614</v>
       </c>
       <c r="P50">
-        <v>11.780569472</v>
+        <v>11.596362586</v>
       </c>
       <c r="Q50">
-        <v>11.780569472</v>
+        <v>11.596362586</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1351023697366767</v>
+        <v>0.1365709469494924</v>
       </c>
       <c r="T50">
-        <v>1.635604263424089</v>
+        <v>1.662501770819822</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.332352638905511</v>
+        <v>2.28475360545846</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09676484294424113</v>
+        <v>0.09671613362541037</v>
       </c>
       <c r="C51">
-        <v>152.716716395358</v>
+        <v>149.6571473270857</v>
       </c>
       <c r="D51">
-        <v>281.637716395358</v>
+        <v>281.9071473270857</v>
       </c>
       <c r="E51">
-        <v>14.82099999999997</v>
+        <v>18.14999999999998</v>
       </c>
       <c r="F51">
-        <v>163.121</v>
+        <v>166.45</v>
       </c>
       <c r="G51">
         <v>34.2</v>
@@ -5469,28 +5469,28 @@
         <v>28.25</v>
       </c>
       <c r="M51">
-        <v>12.3645718</v>
+        <v>12.61691</v>
       </c>
       <c r="N51">
-        <v>15.8854282</v>
+        <v>15.63309</v>
       </c>
       <c r="O51">
-        <v>4.289065614</v>
+        <v>4.2209343</v>
       </c>
       <c r="P51">
-        <v>11.596362586</v>
+        <v>11.4121557</v>
       </c>
       <c r="Q51">
-        <v>11.596362586</v>
+        <v>11.4121557</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1365709469494924</v>
+        <v>0.1380982672508207</v>
       </c>
       <c r="T51">
-        <v>1.662501770819822</v>
+        <v>1.690475178511386</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.28475360545846</v>
+        <v>2.239058533349291</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09671613362541037</v>
+        <v>0.09666742430657962</v>
       </c>
       <c r="C52">
-        <v>149.6571473270857</v>
+        <v>146.5980942588797</v>
       </c>
       <c r="D52">
-        <v>281.9071473270857</v>
+        <v>282.1770942588797</v>
       </c>
       <c r="E52">
-        <v>18.14999999999998</v>
+        <v>21.47899999999998</v>
       </c>
       <c r="F52">
-        <v>166.45</v>
+        <v>169.779</v>
       </c>
       <c r="G52">
         <v>34.2</v>
@@ -5551,28 +5551,28 @@
         <v>28.25</v>
       </c>
       <c r="M52">
-        <v>12.61691</v>
+        <v>12.8692482</v>
       </c>
       <c r="N52">
-        <v>15.63309</v>
+        <v>15.3807518</v>
       </c>
       <c r="O52">
-        <v>4.2209343</v>
+        <v>4.152802986</v>
       </c>
       <c r="P52">
-        <v>11.4121557</v>
+        <v>11.227948814</v>
       </c>
       <c r="Q52">
-        <v>11.4121557</v>
+        <v>11.227948814</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1380982672508207</v>
+        <v>0.1396879271562849</v>
       </c>
       <c r="T52">
-        <v>1.690475178511386</v>
+        <v>1.719590357945462</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.239058533349291</v>
+        <v>2.195155424852246</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09666742430657962</v>
+        <v>0.09661871498774885</v>
       </c>
       <c r="C53">
-        <v>146.5980942588797</v>
+        <v>143.5395586744854</v>
       </c>
       <c r="D53">
-        <v>282.1770942588797</v>
+        <v>282.4475586744854</v>
       </c>
       <c r="E53">
-        <v>21.47899999999998</v>
+        <v>24.80799999999999</v>
       </c>
       <c r="F53">
-        <v>169.779</v>
+        <v>173.108</v>
       </c>
       <c r="G53">
         <v>34.2</v>
@@ -5633,28 +5633,28 @@
         <v>28.25</v>
       </c>
       <c r="M53">
-        <v>12.8692482</v>
+        <v>13.1215864</v>
       </c>
       <c r="N53">
-        <v>15.3807518</v>
+        <v>15.1284136</v>
       </c>
       <c r="O53">
-        <v>4.152802986</v>
+        <v>4.084671672</v>
       </c>
       <c r="P53">
-        <v>11.227948814</v>
+        <v>11.043741928</v>
       </c>
       <c r="Q53">
-        <v>11.227948814</v>
+        <v>11.043741928</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1396879271562849</v>
+        <v>0.1413438228911434</v>
       </c>
       <c r="T53">
-        <v>1.719590357945462</v>
+        <v>1.749918669855958</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.195155424852246</v>
+        <v>2.152940897451241</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09661871498774885</v>
+        <v>0.0965700056689181</v>
       </c>
       <c r="C54">
-        <v>143.5395586744854</v>
+        <v>140.4815420633422</v>
       </c>
       <c r="D54">
-        <v>282.4475586744854</v>
+        <v>282.7185420633422</v>
       </c>
       <c r="E54">
-        <v>24.80799999999999</v>
+        <v>28.13699999999997</v>
       </c>
       <c r="F54">
-        <v>173.108</v>
+        <v>176.437</v>
       </c>
       <c r="G54">
         <v>34.2</v>
@@ -5715,28 +5715,28 @@
         <v>28.25</v>
       </c>
       <c r="M54">
-        <v>13.1215864</v>
+        <v>13.3739246</v>
       </c>
       <c r="N54">
-        <v>15.1284136</v>
+        <v>14.8760754</v>
       </c>
       <c r="O54">
-        <v>4.084671672</v>
+        <v>4.016540358</v>
       </c>
       <c r="P54">
-        <v>11.043741928</v>
+        <v>10.859535042</v>
       </c>
       <c r="Q54">
-        <v>11.043741928</v>
+        <v>10.859535042</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1413438228911434</v>
+        <v>0.1430701822742938</v>
       </c>
       <c r="T54">
-        <v>1.749918669855958</v>
+        <v>1.78153754823073</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.152940897451241</v>
+        <v>2.112319371084237</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0965700056689181</v>
+        <v>0.09652129635008733</v>
       </c>
       <c r="C55">
-        <v>140.4815420633422</v>
+        <v>137.4240459206112</v>
       </c>
       <c r="D55">
-        <v>282.7185420633422</v>
+        <v>282.9900459206112</v>
       </c>
       <c r="E55">
-        <v>28.13699999999997</v>
+        <v>31.46599999999998</v>
       </c>
       <c r="F55">
-        <v>176.437</v>
+        <v>179.766</v>
       </c>
       <c r="G55">
         <v>34.2</v>
@@ -5797,28 +5797,28 @@
         <v>28.25</v>
       </c>
       <c r="M55">
-        <v>13.3739246</v>
+        <v>13.6262628</v>
       </c>
       <c r="N55">
-        <v>14.8760754</v>
+        <v>14.6237372</v>
       </c>
       <c r="O55">
-        <v>4.016540358</v>
+        <v>3.948409044</v>
       </c>
       <c r="P55">
-        <v>10.859535042</v>
+        <v>10.675328156</v>
       </c>
       <c r="Q55">
-        <v>10.859535042</v>
+        <v>10.675328156</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1430701822742938</v>
+        <v>0.1448716007610594</v>
       </c>
       <c r="T55">
-        <v>1.78153754823073</v>
+        <v>1.814531160447884</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.112319371084237</v>
+        <v>2.073202345693788</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09652129635008733</v>
+        <v>0.09647258703125658</v>
       </c>
       <c r="C56">
-        <v>137.4240459206112</v>
+        <v>134.3670717472021</v>
       </c>
       <c r="D56">
-        <v>282.9900459206112</v>
+        <v>283.2620717472021</v>
       </c>
       <c r="E56">
-        <v>31.46599999999998</v>
+        <v>34.79499999999999</v>
       </c>
       <c r="F56">
-        <v>179.766</v>
+        <v>183.095</v>
       </c>
       <c r="G56">
         <v>34.2</v>
@@ -5879,28 +5879,28 @@
         <v>28.25</v>
       </c>
       <c r="M56">
-        <v>13.6262628</v>
+        <v>13.878601</v>
       </c>
       <c r="N56">
-        <v>14.6237372</v>
+        <v>14.371399</v>
       </c>
       <c r="O56">
-        <v>3.948409044</v>
+        <v>3.88027773</v>
       </c>
       <c r="P56">
-        <v>10.675328156</v>
+        <v>10.49112127</v>
       </c>
       <c r="Q56">
-        <v>10.675328156</v>
+        <v>10.49112127</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1448716007610594</v>
+        <v>0.1467530822916813</v>
       </c>
       <c r="T56">
-        <v>1.814531160447884</v>
+        <v>1.848991155430244</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.073202345693788</v>
+        <v>2.035507757590264</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09647258703125658</v>
+        <v>0.1022288377124258</v>
       </c>
       <c r="C57">
-        <v>134.3670717472021</v>
+        <v>102.1427841682912</v>
       </c>
       <c r="D57">
-        <v>283.2620717472021</v>
+        <v>254.3667841682912</v>
       </c>
       <c r="E57">
-        <v>34.79499999999999</v>
+        <v>38.124</v>
       </c>
       <c r="F57">
-        <v>183.095</v>
+        <v>186.424</v>
       </c>
       <c r="G57">
         <v>34.2</v>
@@ -5961,45 +5961,45 @@
         <v>28.25</v>
       </c>
       <c r="M57">
-        <v>13.878601</v>
+        <v>16.77816</v>
       </c>
       <c r="N57">
-        <v>14.371399</v>
+        <v>11.47184</v>
       </c>
       <c r="O57">
-        <v>3.88027773</v>
+        <v>3.0973968</v>
       </c>
       <c r="P57">
-        <v>10.49112127</v>
+        <v>8.3744432</v>
       </c>
       <c r="Q57">
-        <v>10.49112127</v>
+        <v>8.3744432</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1467530822916813</v>
+        <v>0.1487200857100587</v>
       </c>
       <c r="T57">
-        <v>1.848991155430244</v>
+        <v>1.885017513820894</v>
       </c>
       <c r="U57">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V57">
         <v>0.27</v>
       </c>
       <c r="W57">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.035507757590264</v>
+        <v>1.683736476467026</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1022288377124258</v>
+        <v>0.1022837883935951</v>
       </c>
       <c r="C58">
-        <v>102.1427841682912</v>
+        <v>98.56632151653915</v>
       </c>
       <c r="D58">
-        <v>254.3667841682912</v>
+        <v>254.1193215165391</v>
       </c>
       <c r="E58">
-        <v>38.124</v>
+        <v>41.453</v>
       </c>
       <c r="F58">
-        <v>186.424</v>
+        <v>189.753</v>
       </c>
       <c r="G58">
         <v>34.2</v>
@@ -6043,28 +6043,28 @@
         <v>28.25</v>
       </c>
       <c r="M58">
-        <v>16.77816</v>
+        <v>17.07777</v>
       </c>
       <c r="N58">
-        <v>11.47184</v>
+        <v>11.17223</v>
       </c>
       <c r="O58">
-        <v>3.0973968</v>
+        <v>3.0165021</v>
       </c>
       <c r="P58">
-        <v>8.3744432</v>
+        <v>8.155727899999999</v>
       </c>
       <c r="Q58">
-        <v>8.3744432</v>
+        <v>8.155727899999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1487200857100587</v>
+        <v>0.1507785776595234</v>
       </c>
       <c r="T58">
-        <v>1.885017513820894</v>
+        <v>1.922719516787853</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.683736476467026</v>
+        <v>1.65419724003778</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1022837883935951</v>
+        <v>0.1023387390747643</v>
       </c>
       <c r="C59">
-        <v>98.56632151653915</v>
+        <v>94.99033988864798</v>
       </c>
       <c r="D59">
-        <v>254.1193215165391</v>
+        <v>253.872339888648</v>
       </c>
       <c r="E59">
-        <v>41.453</v>
+        <v>44.78200000000001</v>
       </c>
       <c r="F59">
-        <v>189.753</v>
+        <v>193.082</v>
       </c>
       <c r="G59">
         <v>34.2</v>
@@ -6125,28 +6125,28 @@
         <v>28.25</v>
       </c>
       <c r="M59">
-        <v>17.07777</v>
+        <v>17.37738</v>
       </c>
       <c r="N59">
-        <v>11.17223</v>
+        <v>10.87262</v>
       </c>
       <c r="O59">
-        <v>3.0165021</v>
+        <v>2.935607399999999</v>
       </c>
       <c r="P59">
-        <v>8.155727899999999</v>
+        <v>7.937012599999998</v>
       </c>
       <c r="Q59">
-        <v>8.155727899999999</v>
+        <v>7.937012599999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1507785776595234</v>
+        <v>0.1529350930351531</v>
       </c>
       <c r="T59">
-        <v>1.922719516787853</v>
+        <v>1.962216853229429</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.65419724003778</v>
+        <v>1.625676597968163</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1023387390747643</v>
+        <v>0.1023936897559335</v>
       </c>
       <c r="C60">
-        <v>94.99033988864804</v>
+        <v>91.41483788344092</v>
       </c>
       <c r="D60">
-        <v>253.872339888648</v>
+        <v>253.6258378834409</v>
       </c>
       <c r="E60">
-        <v>44.78199999999995</v>
+        <v>48.11099999999996</v>
       </c>
       <c r="F60">
-        <v>193.082</v>
+        <v>196.411</v>
       </c>
       <c r="G60">
         <v>34.2</v>
@@ -6207,28 +6207,28 @@
         <v>28.25</v>
       </c>
       <c r="M60">
-        <v>17.37738</v>
+        <v>17.67699</v>
       </c>
       <c r="N60">
-        <v>10.87262</v>
+        <v>10.57301</v>
       </c>
       <c r="O60">
-        <v>2.935607400000002</v>
+        <v>2.854712700000001</v>
       </c>
       <c r="P60">
-        <v>7.937012600000003</v>
+        <v>7.718297300000002</v>
       </c>
       <c r="Q60">
-        <v>7.937012600000003</v>
+        <v>7.718297300000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.152935093035153</v>
+        <v>0.1551968042827647</v>
       </c>
       <c r="T60">
-        <v>1.962216853229428</v>
+        <v>2.003640889009618</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.625676597968164</v>
+        <v>1.598122757324635</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1023936897559335</v>
+        <v>0.1024486404371028</v>
       </c>
       <c r="C61">
-        <v>91.41483788344092</v>
+        <v>87.83981410517768</v>
       </c>
       <c r="D61">
-        <v>253.6258378834409</v>
+        <v>253.3798141051776</v>
       </c>
       <c r="E61">
-        <v>48.11099999999996</v>
+        <v>51.43999999999997</v>
       </c>
       <c r="F61">
-        <v>196.411</v>
+        <v>199.74</v>
       </c>
       <c r="G61">
         <v>34.2</v>
@@ -6289,28 +6289,28 @@
         <v>28.25</v>
       </c>
       <c r="M61">
-        <v>17.67699</v>
+        <v>17.9766</v>
       </c>
       <c r="N61">
-        <v>10.57301</v>
+        <v>10.2734</v>
       </c>
       <c r="O61">
-        <v>2.854712700000001</v>
+        <v>2.773818000000001</v>
       </c>
       <c r="P61">
-        <v>7.718297300000002</v>
+        <v>7.499582000000002</v>
       </c>
       <c r="Q61">
-        <v>7.718297300000002</v>
+        <v>7.499582000000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1551968042827647</v>
+        <v>0.1575716010927569</v>
       </c>
       <c r="T61">
-        <v>2.003640889009618</v>
+        <v>2.047136126578816</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.598122757324635</v>
+        <v>1.571487378035891</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1024486404371028</v>
+        <v>0.102503591118272</v>
       </c>
       <c r="C62">
-        <v>87.83981410517768</v>
+        <v>84.26526716352842</v>
       </c>
       <c r="D62">
-        <v>253.3798141051776</v>
+        <v>253.1342671635284</v>
       </c>
       <c r="E62">
-        <v>51.43999999999997</v>
+        <v>54.76899999999998</v>
       </c>
       <c r="F62">
-        <v>199.74</v>
+        <v>203.069</v>
       </c>
       <c r="G62">
         <v>34.2</v>
@@ -6371,28 +6371,28 @@
         <v>28.25</v>
       </c>
       <c r="M62">
-        <v>17.9766</v>
+        <v>18.27621</v>
       </c>
       <c r="N62">
-        <v>10.2734</v>
+        <v>9.973790000000001</v>
       </c>
       <c r="O62">
-        <v>2.773818000000001</v>
+        <v>2.6929233</v>
       </c>
       <c r="P62">
-        <v>7.499582000000002</v>
+        <v>7.280866700000001</v>
       </c>
       <c r="Q62">
-        <v>7.499582000000002</v>
+        <v>7.280866700000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1575716010927569</v>
+        <v>0.1600681823545436</v>
       </c>
       <c r="T62">
-        <v>2.047136126578816</v>
+        <v>2.092861889151564</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.571487378035891</v>
+        <v>1.545725289871368</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.102503591118272</v>
+        <v>0.1025585417994413</v>
       </c>
       <c r="C63">
-        <v>84.26526716352842</v>
+        <v>80.69119567354787</v>
       </c>
       <c r="D63">
-        <v>253.1342671635284</v>
+        <v>252.8891956735479</v>
       </c>
       <c r="E63">
-        <v>54.76899999999998</v>
+        <v>58.09799999999998</v>
       </c>
       <c r="F63">
-        <v>203.069</v>
+        <v>206.398</v>
       </c>
       <c r="G63">
         <v>34.2</v>
@@ -6453,28 +6453,28 @@
         <v>28.25</v>
       </c>
       <c r="M63">
-        <v>18.27621</v>
+        <v>18.57582</v>
       </c>
       <c r="N63">
-        <v>9.973790000000001</v>
+        <v>9.67418</v>
       </c>
       <c r="O63">
-        <v>2.6929233</v>
+        <v>2.6120286</v>
       </c>
       <c r="P63">
-        <v>7.280866700000001</v>
+        <v>7.062151399999999</v>
       </c>
       <c r="Q63">
-        <v>7.280866700000001</v>
+        <v>7.062151399999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1600681823545436</v>
+        <v>0.1626961626301086</v>
       </c>
       <c r="T63">
-        <v>2.092861889151564</v>
+        <v>2.140994270807088</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.545725289871368</v>
+        <v>1.520794236808927</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1025585417994413</v>
+        <v>0.1315422897101107</v>
       </c>
       <c r="C64">
-        <v>80.69119567354787</v>
+        <v>-8.122770047746087</v>
       </c>
       <c r="D64">
-        <v>252.8891956735479</v>
+        <v>167.4042299522539</v>
       </c>
       <c r="E64">
-        <v>58.09799999999998</v>
+        <v>61.42699999999996</v>
       </c>
       <c r="F64">
-        <v>206.398</v>
+        <v>209.727</v>
       </c>
       <c r="G64">
         <v>34.2</v>
@@ -6535,45 +6535,45 @@
         <v>28.25</v>
       </c>
       <c r="M64">
-        <v>18.57582</v>
+        <v>30.7879236</v>
       </c>
       <c r="N64">
-        <v>9.67418</v>
+        <v>-2.537923599999999</v>
       </c>
       <c r="O64">
-        <v>2.6120286</v>
+        <v>-0.6852393719999998</v>
       </c>
       <c r="P64">
-        <v>7.062151399999999</v>
+        <v>-1.852684227999999</v>
       </c>
       <c r="Q64">
-        <v>7.062151399999999</v>
+        <v>-1.852684227999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1626961626301086</v>
+        <v>0.1674880423834432</v>
       </c>
       <c r="T64">
-        <v>2.140994270807088</v>
+        <v>2.228759231328072</v>
       </c>
       <c r="U64">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.27</v>
+        <v>0.2477432417689902</v>
       </c>
       <c r="W64">
-        <v>0.06569999999999999</v>
+        <v>0.1104312921083122</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.520794236808927</v>
+        <v>0.9175675621073712</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1315422897101107</v>
+        <v>0.1325522897101107</v>
       </c>
       <c r="C65">
-        <v>-8.122770047746087</v>
+        <v>-13.40074768069115</v>
       </c>
       <c r="D65">
-        <v>167.4042299522539</v>
+        <v>165.4552523193088</v>
       </c>
       <c r="E65">
-        <v>61.42699999999996</v>
+        <v>64.75599999999997</v>
       </c>
       <c r="F65">
-        <v>209.727</v>
+        <v>213.056</v>
       </c>
       <c r="G65">
         <v>34.2</v>
@@ -6617,37 +6617,37 @@
         <v>28.25</v>
       </c>
       <c r="M65">
-        <v>30.7879236</v>
+        <v>31.2766208</v>
       </c>
       <c r="N65">
-        <v>-2.537923599999999</v>
+        <v>-3.0266208</v>
       </c>
       <c r="O65">
-        <v>-0.6852393719999998</v>
+        <v>-0.817187616</v>
       </c>
       <c r="P65">
-        <v>-1.852684227999999</v>
+        <v>-2.209433184</v>
       </c>
       <c r="Q65">
-        <v>-1.852684227999999</v>
+        <v>-2.209433184</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1674880423834432</v>
+        <v>0.1708682657829833</v>
       </c>
       <c r="T65">
-        <v>2.228759231328072</v>
+        <v>2.290669209976075</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2477432417689902</v>
+        <v>0.2438722536163498</v>
       </c>
       <c r="W65">
-        <v>0.1104312921083122</v>
+        <v>0.1109995531691199</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9175675621073712</v>
+        <v>0.9032305689494435</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1325522897101107</v>
+        <v>0.1335622897101107</v>
       </c>
       <c r="C66">
-        <v>-13.40074768069115</v>
+        <v>-18.63386624225654</v>
       </c>
       <c r="D66">
-        <v>165.4552523193088</v>
+        <v>163.5511337577434</v>
       </c>
       <c r="E66">
-        <v>64.75599999999997</v>
+        <v>68.08499999999998</v>
       </c>
       <c r="F66">
-        <v>213.056</v>
+        <v>216.385</v>
       </c>
       <c r="G66">
         <v>34.2</v>
@@ -6699,37 +6699,37 @@
         <v>28.25</v>
       </c>
       <c r="M66">
-        <v>31.2766208</v>
+        <v>31.765318</v>
       </c>
       <c r="N66">
-        <v>-3.0266208</v>
+        <v>-3.515318000000001</v>
       </c>
       <c r="O66">
-        <v>-0.817187616</v>
+        <v>-0.9491358600000003</v>
       </c>
       <c r="P66">
-        <v>-2.209433184</v>
+        <v>-2.56618214</v>
       </c>
       <c r="Q66">
-        <v>-2.209433184</v>
+        <v>-2.56618214</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1708682657829833</v>
+        <v>0.1744416448053543</v>
       </c>
       <c r="T66">
-        <v>2.290669209976075</v>
+        <v>2.356116901689676</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2438722536163498</v>
+        <v>0.2401203727914829</v>
       </c>
       <c r="W66">
-        <v>0.1109995531691199</v>
+        <v>0.1115503292742103</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9032305689494435</v>
+        <v>0.889334714042529</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1335622897101107</v>
+        <v>0.1345722897101107</v>
       </c>
       <c r="C67">
-        <v>-18.63386624225654</v>
+        <v>-23.82365687449942</v>
       </c>
       <c r="D67">
-        <v>163.5511337577434</v>
+        <v>161.6903431255006</v>
       </c>
       <c r="E67">
-        <v>68.08499999999998</v>
+        <v>71.41399999999999</v>
       </c>
       <c r="F67">
-        <v>216.385</v>
+        <v>219.714</v>
       </c>
       <c r="G67">
         <v>34.2</v>
@@ -6781,37 +6781,37 @@
         <v>28.25</v>
       </c>
       <c r="M67">
-        <v>31.765318</v>
+        <v>32.2540152</v>
       </c>
       <c r="N67">
-        <v>-3.515318000000001</v>
+        <v>-4.004015200000005</v>
       </c>
       <c r="O67">
-        <v>-0.9491358600000003</v>
+        <v>-1.081084104000001</v>
       </c>
       <c r="P67">
-        <v>-2.56618214</v>
+        <v>-2.922931096000004</v>
       </c>
       <c r="Q67">
-        <v>-2.56618214</v>
+        <v>-2.922931096000004</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1744416448053543</v>
+        <v>0.178225222593747</v>
       </c>
       <c r="T67">
-        <v>2.356116901689676</v>
+        <v>2.425414457621726</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2401203727914829</v>
+        <v>0.2364821853249452</v>
       </c>
       <c r="W67">
-        <v>0.1115503292742103</v>
+        <v>0.112084415194298</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.889334714042529</v>
+        <v>0.8758599456479451</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1345722897101107</v>
+        <v>0.1355822897101107</v>
       </c>
       <c r="C68">
-        <v>-23.82365687449942</v>
+        <v>-28.97158182154686</v>
       </c>
       <c r="D68">
-        <v>161.6903431255006</v>
+        <v>159.8714181784532</v>
       </c>
       <c r="E68">
-        <v>71.41399999999999</v>
+        <v>74.74299999999999</v>
       </c>
       <c r="F68">
-        <v>219.714</v>
+        <v>223.043</v>
       </c>
       <c r="G68">
         <v>34.2</v>
@@ -6863,37 +6863,37 @@
         <v>28.25</v>
       </c>
       <c r="M68">
-        <v>32.2540152</v>
+        <v>32.7427124</v>
       </c>
       <c r="N68">
-        <v>-4.004015200000005</v>
+        <v>-4.492712400000002</v>
       </c>
       <c r="O68">
-        <v>-1.081084104000001</v>
+        <v>-1.213032348000001</v>
       </c>
       <c r="P68">
-        <v>-2.922931096000004</v>
+        <v>-3.279680052000002</v>
       </c>
       <c r="Q68">
-        <v>-2.922931096000004</v>
+        <v>-3.279680052000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.178225222593747</v>
+        <v>0.1822381081268909</v>
       </c>
       <c r="T68">
-        <v>2.425414457621726</v>
+        <v>2.498911865428445</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2364821853249452</v>
+        <v>0.232952600469349</v>
       </c>
       <c r="W68">
-        <v>0.112084415194298</v>
+        <v>0.1126025582510996</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8758599456479451</v>
+        <v>0.862787409145737</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1355822897101107</v>
+        <v>0.1365922897101107</v>
       </c>
       <c r="C69">
-        <v>-28.97158182154686</v>
+        <v>-34.07903826179961</v>
       </c>
       <c r="D69">
-        <v>159.8714181784532</v>
+        <v>158.0929617382004</v>
       </c>
       <c r="E69">
-        <v>74.74299999999999</v>
+        <v>78.072</v>
       </c>
       <c r="F69">
-        <v>223.043</v>
+        <v>226.372</v>
       </c>
       <c r="G69">
         <v>34.2</v>
@@ -6945,37 +6945,37 @@
         <v>28.25</v>
       </c>
       <c r="M69">
-        <v>32.7427124</v>
+        <v>33.23140960000001</v>
       </c>
       <c r="N69">
-        <v>-4.492712400000002</v>
+        <v>-4.981409600000006</v>
       </c>
       <c r="O69">
-        <v>-1.213032348000001</v>
+        <v>-1.344980592000002</v>
       </c>
       <c r="P69">
-        <v>-3.279680052000002</v>
+        <v>-3.636429008000005</v>
       </c>
       <c r="Q69">
-        <v>-3.279680052000002</v>
+        <v>-3.636429008000005</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1822381081268909</v>
+        <v>0.1865017990058563</v>
       </c>
       <c r="T69">
-        <v>2.498911865428445</v>
+        <v>2.577002861223084</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.232952600469349</v>
+        <v>0.229526826933035</v>
       </c>
       <c r="W69">
-        <v>0.1126025582510996</v>
+        <v>0.1131054618062305</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.862787409145737</v>
+        <v>0.8500993590112408</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1365922897101107</v>
+        <v>0.1376022897101107</v>
       </c>
       <c r="C70">
-        <v>-34.07903826179961</v>
+        <v>-39.14736188716657</v>
       </c>
       <c r="D70">
-        <v>158.0929617382004</v>
+        <v>156.3536381128334</v>
       </c>
       <c r="E70">
-        <v>78.072</v>
+        <v>81.40099999999998</v>
       </c>
       <c r="F70">
-        <v>226.372</v>
+        <v>229.701</v>
       </c>
       <c r="G70">
         <v>34.2</v>
@@ -7027,37 +7027,37 @@
         <v>28.25</v>
       </c>
       <c r="M70">
-        <v>33.23140960000001</v>
+        <v>33.7201068</v>
       </c>
       <c r="N70">
-        <v>-4.981409600000006</v>
+        <v>-5.470106800000003</v>
       </c>
       <c r="O70">
-        <v>-1.344980592000002</v>
+        <v>-1.476928836000001</v>
       </c>
       <c r="P70">
-        <v>-3.636429008000005</v>
+        <v>-3.993177964000003</v>
       </c>
       <c r="Q70">
-        <v>-3.636429008000005</v>
+        <v>-3.993177964000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1865017990058563</v>
+        <v>0.1910405667157226</v>
       </c>
       <c r="T70">
-        <v>2.577002861223084</v>
+        <v>2.660131985778667</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.229526826933035</v>
+        <v>0.2262003511803824</v>
       </c>
       <c r="W70">
-        <v>0.1131054618062305</v>
+        <v>0.1135937884467199</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8500993590112408</v>
+        <v>0.8377790784458605</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1376022897101107</v>
+        <v>0.1386122897101107</v>
       </c>
       <c r="C71">
-        <v>-39.14736188716657</v>
+        <v>-44.17783024860009</v>
       </c>
       <c r="D71">
-        <v>156.3536381128334</v>
+        <v>154.6521697513999</v>
       </c>
       <c r="E71">
-        <v>81.40099999999998</v>
+        <v>84.72999999999999</v>
       </c>
       <c r="F71">
-        <v>229.701</v>
+        <v>233.03</v>
       </c>
       <c r="G71">
         <v>34.2</v>
@@ -7109,37 +7109,37 @@
         <v>28.25</v>
       </c>
       <c r="M71">
-        <v>33.7201068</v>
+        <v>34.208804</v>
       </c>
       <c r="N71">
-        <v>-5.470106800000003</v>
+        <v>-5.958804000000001</v>
       </c>
       <c r="O71">
-        <v>-1.476928836000001</v>
+        <v>-1.60887708</v>
       </c>
       <c r="P71">
-        <v>-3.993177964000003</v>
+        <v>-4.349926920000001</v>
       </c>
       <c r="Q71">
-        <v>-3.993177964000003</v>
+        <v>-4.349926920000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1910405667157226</v>
+        <v>0.19588191893958</v>
       </c>
       <c r="T71">
-        <v>2.660131985778667</v>
+        <v>2.74880305197129</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2262003511803824</v>
+        <v>0.2229689175920912</v>
       </c>
       <c r="W71">
-        <v>0.1135937884467199</v>
+        <v>0.114068162897481</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8377790784458605</v>
+        <v>0.825810805896634</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1386122897101107</v>
+        <v>0.1396222897101107</v>
       </c>
       <c r="C72">
-        <v>-44.17783024860009</v>
+        <v>-49.17166588554247</v>
       </c>
       <c r="D72">
-        <v>154.6521697513999</v>
+        <v>152.9873341144576</v>
       </c>
       <c r="E72">
-        <v>84.72999999999999</v>
+        <v>88.059</v>
       </c>
       <c r="F72">
-        <v>233.03</v>
+        <v>236.359</v>
       </c>
       <c r="G72">
         <v>34.2</v>
@@ -7191,37 +7191,37 @@
         <v>28.25</v>
       </c>
       <c r="M72">
-        <v>34.208804</v>
+        <v>34.6975012</v>
       </c>
       <c r="N72">
-        <v>-5.958804000000001</v>
+        <v>-6.447501200000005</v>
       </c>
       <c r="O72">
-        <v>-1.60887708</v>
+        <v>-1.740825324000001</v>
       </c>
       <c r="P72">
-        <v>-4.349926920000001</v>
+        <v>-4.706675876000004</v>
       </c>
       <c r="Q72">
-        <v>-4.349926920000001</v>
+        <v>-4.706675876000004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.19588191893958</v>
+        <v>0.2010571575237035</v>
       </c>
       <c r="T72">
-        <v>2.74880305197129</v>
+        <v>2.843589364108231</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2229689175920912</v>
+        <v>0.2198285103020617</v>
       </c>
       <c r="W72">
-        <v>0.114068162897481</v>
+        <v>0.1145291746876573</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.825810805896634</v>
+        <v>0.8141796677854138</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1396222897101107</v>
+        <v>0.1406322897101107</v>
       </c>
       <c r="C73">
-        <v>-49.17166588554238</v>
+        <v>-54.13003925539289</v>
       </c>
       <c r="D73">
-        <v>152.9873341144576</v>
+        <v>151.3579607446071</v>
       </c>
       <c r="E73">
-        <v>88.05899999999997</v>
+        <v>91.38799999999998</v>
       </c>
       <c r="F73">
-        <v>236.359</v>
+        <v>239.688</v>
       </c>
       <c r="G73">
         <v>34.2</v>
@@ -7273,37 +7273,37 @@
         <v>28.25</v>
       </c>
       <c r="M73">
-        <v>34.6975012</v>
+        <v>35.1861984</v>
       </c>
       <c r="N73">
-        <v>-6.447501199999998</v>
+        <v>-6.936198400000002</v>
       </c>
       <c r="O73">
-        <v>-1.740825324</v>
+        <v>-1.872773568000001</v>
       </c>
       <c r="P73">
-        <v>-4.706675875999998</v>
+        <v>-5.063424832000002</v>
       </c>
       <c r="Q73">
-        <v>-4.706675875999998</v>
+        <v>-5.063424832000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2010571575237034</v>
+        <v>0.2066020560066928</v>
       </c>
       <c r="T73">
-        <v>2.84358936410823</v>
+        <v>2.945146127112095</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2198285103020618</v>
+        <v>0.2167753365478665</v>
       </c>
       <c r="W73">
-        <v>0.1145291746876573</v>
+        <v>0.1149773805947732</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.814179667785414</v>
+        <v>0.8028716168439498</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1406322897101107</v>
+        <v>0.1833016288027104</v>
       </c>
       <c r="C74">
-        <v>-54.13003925539289</v>
+        <v>-104.4282585120067</v>
       </c>
       <c r="D74">
-        <v>151.3579607446071</v>
+        <v>104.3887414879933</v>
       </c>
       <c r="E74">
-        <v>91.38799999999998</v>
+        <v>94.71699999999996</v>
       </c>
       <c r="F74">
-        <v>239.688</v>
+        <v>243.017</v>
       </c>
       <c r="G74">
         <v>34.2</v>
@@ -7355,45 +7355,45 @@
         <v>28.25</v>
       </c>
       <c r="M74">
-        <v>35.1861984</v>
+        <v>48.7978136</v>
       </c>
       <c r="N74">
-        <v>-6.936198400000002</v>
+        <v>-20.5478136</v>
       </c>
       <c r="O74">
-        <v>-1.872773568000001</v>
+        <v>-5.547909671999999</v>
       </c>
       <c r="P74">
-        <v>-5.063424832000002</v>
+        <v>-14.999903928</v>
       </c>
       <c r="Q74">
-        <v>-5.063424832000002</v>
+        <v>-14.999903928</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2066020560066928</v>
+        <v>0.2208515362017544</v>
       </c>
       <c r="T74">
-        <v>2.945146127112095</v>
+        <v>3.206130361095393</v>
       </c>
       <c r="U74">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.2167753365478665</v>
+        <v>0.1563082326295045</v>
       </c>
       <c r="W74">
-        <v>0.1149773805947732</v>
+        <v>0.1694133068879955</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.8028716168439498</v>
+        <v>0.578919380109276</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1833016288027104</v>
+        <v>0.1848516288027104</v>
       </c>
       <c r="C75">
-        <v>-104.4282585120067</v>
+        <v>-108.920873427557</v>
       </c>
       <c r="D75">
-        <v>104.3887414879933</v>
+        <v>103.225126572443</v>
       </c>
       <c r="E75">
-        <v>94.71699999999996</v>
+        <v>98.04599999999996</v>
       </c>
       <c r="F75">
-        <v>243.017</v>
+        <v>246.346</v>
       </c>
       <c r="G75">
         <v>34.2</v>
@@ -7437,37 +7437,37 @@
         <v>28.25</v>
       </c>
       <c r="M75">
-        <v>48.7978136</v>
+        <v>49.4662768</v>
       </c>
       <c r="N75">
-        <v>-20.5478136</v>
+        <v>-21.2162768</v>
       </c>
       <c r="O75">
-        <v>-5.547909671999999</v>
+        <v>-5.728394735999999</v>
       </c>
       <c r="P75">
-        <v>-14.999903928</v>
+        <v>-15.487882064</v>
       </c>
       <c r="Q75">
-        <v>-14.999903928</v>
+        <v>-15.487882064</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2208515362017544</v>
+        <v>0.2275842875941295</v>
       </c>
       <c r="T75">
-        <v>3.206130361095393</v>
+        <v>3.32944306729137</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1563082326295045</v>
+        <v>0.1541959592155923</v>
       </c>
       <c r="W75">
-        <v>0.1694133068879955</v>
+        <v>0.1698374513895091</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.578919380109276</v>
+        <v>0.5710961452429345</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1848516288027104</v>
+        <v>0.1864016288027104</v>
       </c>
       <c r="C76">
-        <v>-108.920873427557</v>
+        <v>-113.3878328349248</v>
       </c>
       <c r="D76">
-        <v>103.225126572443</v>
+        <v>102.0871671650752</v>
       </c>
       <c r="E76">
-        <v>98.04599999999996</v>
+        <v>101.375</v>
       </c>
       <c r="F76">
-        <v>246.346</v>
+        <v>249.675</v>
       </c>
       <c r="G76">
         <v>34.2</v>
@@ -7519,37 +7519,37 @@
         <v>28.25</v>
       </c>
       <c r="M76">
-        <v>49.4662768</v>
+        <v>50.13474</v>
       </c>
       <c r="N76">
-        <v>-21.2162768</v>
+        <v>-21.88474</v>
       </c>
       <c r="O76">
-        <v>-5.728394735999999</v>
+        <v>-5.9088798</v>
       </c>
       <c r="P76">
-        <v>-15.487882064</v>
+        <v>-15.9758602</v>
       </c>
       <c r="Q76">
-        <v>-15.487882064</v>
+        <v>-15.9758602</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2275842875941295</v>
+        <v>0.2348556590978947</v>
       </c>
       <c r="T76">
-        <v>3.32944306729137</v>
+        <v>3.462620789983025</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1541959592155923</v>
+        <v>0.1521400130927178</v>
       </c>
       <c r="W76">
-        <v>0.1698374513895091</v>
+        <v>0.1702502853709823</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5710961452429345</v>
+        <v>0.5634815299730287</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1864016288027104</v>
+        <v>0.1879516288027104</v>
       </c>
       <c r="C77">
-        <v>-113.3878328349248</v>
+        <v>-117.8299759655285</v>
       </c>
       <c r="D77">
-        <v>102.0871671650752</v>
+        <v>100.9740240344715</v>
       </c>
       <c r="E77">
-        <v>101.375</v>
+        <v>104.704</v>
       </c>
       <c r="F77">
-        <v>249.675</v>
+        <v>253.004</v>
       </c>
       <c r="G77">
         <v>34.2</v>
@@ -7601,37 +7601,37 @@
         <v>28.25</v>
       </c>
       <c r="M77">
-        <v>50.13474</v>
+        <v>50.8032032</v>
       </c>
       <c r="N77">
-        <v>-21.88474</v>
+        <v>-22.5532032</v>
       </c>
       <c r="O77">
-        <v>-5.9088798</v>
+        <v>-6.089364864</v>
       </c>
       <c r="P77">
-        <v>-15.9758602</v>
+        <v>-16.463838336</v>
       </c>
       <c r="Q77">
-        <v>-15.9758602</v>
+        <v>-16.463838336</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2348556590978947</v>
+        <v>0.2427329782269737</v>
       </c>
       <c r="T77">
-        <v>3.462620789983025</v>
+        <v>3.606896656232318</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1521400130927178</v>
+        <v>0.150138170815182</v>
       </c>
       <c r="W77">
-        <v>0.1702502853709823</v>
+        <v>0.1706522553003115</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5634815299730287</v>
+        <v>0.5560672993154889</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1879516288027104</v>
+        <v>0.1895016288027104</v>
       </c>
       <c r="C78">
-        <v>-117.8299759655285</v>
+        <v>-122.2481058421864</v>
       </c>
       <c r="D78">
-        <v>100.9740240344715</v>
+        <v>99.88489415781358</v>
       </c>
       <c r="E78">
-        <v>104.704</v>
+        <v>108.033</v>
       </c>
       <c r="F78">
-        <v>253.004</v>
+        <v>256.333</v>
       </c>
       <c r="G78">
         <v>34.2</v>
@@ -7683,37 +7683,37 @@
         <v>28.25</v>
       </c>
       <c r="M78">
-        <v>50.8032032</v>
+        <v>51.4716664</v>
       </c>
       <c r="N78">
-        <v>-22.5532032</v>
+        <v>-23.2216664</v>
       </c>
       <c r="O78">
-        <v>-6.089364864</v>
+        <v>-6.269849927999999</v>
       </c>
       <c r="P78">
-        <v>-16.463838336</v>
+        <v>-16.951816472</v>
       </c>
       <c r="Q78">
-        <v>-16.463838336</v>
+        <v>-16.951816472</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2427329782269737</v>
+        <v>0.2512952816281465</v>
       </c>
       <c r="T78">
-        <v>3.606896656232318</v>
+        <v>3.763718249981549</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.150138170815182</v>
+        <v>0.1481883244409589</v>
       </c>
       <c r="W78">
-        <v>0.1706522553003115</v>
+        <v>0.1710437844522555</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5560672993154889</v>
+        <v>0.5488456460776254</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1895016288027104</v>
+        <v>0.1910516288027104</v>
       </c>
       <c r="C79">
-        <v>-122.2481058421864</v>
+        <v>-126.6429912110513</v>
       </c>
       <c r="D79">
-        <v>99.88489415781358</v>
+        <v>98.81900878894864</v>
       </c>
       <c r="E79">
-        <v>108.033</v>
+        <v>111.362</v>
       </c>
       <c r="F79">
-        <v>256.333</v>
+        <v>259.662</v>
       </c>
       <c r="G79">
         <v>34.2</v>
@@ -7765,37 +7765,37 @@
         <v>28.25</v>
       </c>
       <c r="M79">
-        <v>51.4716664</v>
+        <v>52.14012959999999</v>
       </c>
       <c r="N79">
-        <v>-23.2216664</v>
+        <v>-23.89012959999999</v>
       </c>
       <c r="O79">
-        <v>-6.269849927999999</v>
+        <v>-6.450334991999999</v>
       </c>
       <c r="P79">
-        <v>-16.951816472</v>
+        <v>-17.439794608</v>
       </c>
       <c r="Q79">
-        <v>-16.951816472</v>
+        <v>-17.439794608</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2512952816281465</v>
+        <v>0.2606359762476076</v>
       </c>
       <c r="T79">
-        <v>3.763718249981549</v>
+        <v>3.934796352253437</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1481883244409589</v>
+        <v>0.1462884741276133</v>
       </c>
       <c r="W79">
-        <v>0.1710437844522555</v>
+        <v>0.1714252743951753</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5488456460776254</v>
+        <v>0.5418091634356046</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1910516288027104</v>
+        <v>0.1926016288027104</v>
       </c>
       <c r="C80">
-        <v>-126.6429912110513</v>
+        <v>-131.015368351156</v>
       </c>
       <c r="D80">
-        <v>98.81900878894864</v>
+        <v>97.77563164884401</v>
       </c>
       <c r="E80">
-        <v>111.362</v>
+        <v>114.691</v>
       </c>
       <c r="F80">
-        <v>259.662</v>
+        <v>262.991</v>
       </c>
       <c r="G80">
         <v>34.2</v>
@@ -7847,37 +7847,37 @@
         <v>28.25</v>
       </c>
       <c r="M80">
-        <v>52.14012959999999</v>
+        <v>52.8085928</v>
       </c>
       <c r="N80">
-        <v>-23.89012959999999</v>
+        <v>-24.5585928</v>
       </c>
       <c r="O80">
-        <v>-6.450334991999999</v>
+        <v>-6.630820056</v>
       </c>
       <c r="P80">
-        <v>-17.439794608</v>
+        <v>-17.927772744</v>
       </c>
       <c r="Q80">
-        <v>-17.439794608</v>
+        <v>-17.927772744</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2606359762476076</v>
+        <v>0.2708662608308272</v>
       </c>
       <c r="T80">
-        <v>3.934796352253437</v>
+        <v>4.12216760712265</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1462884741276133</v>
+        <v>0.1444367212905548</v>
       </c>
       <c r="W80">
-        <v>0.1714252743951753</v>
+        <v>0.1717971063648566</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5418091634356046</v>
+        <v>0.5349508195946475</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1926016288027104</v>
+        <v>0.1941516288027104</v>
       </c>
       <c r="C81">
-        <v>-131.015368351156</v>
+        <v>-135.3659427705192</v>
       </c>
       <c r="D81">
-        <v>97.77563164884401</v>
+        <v>96.75405722948085</v>
       </c>
       <c r="E81">
-        <v>114.691</v>
+        <v>118.02</v>
       </c>
       <c r="F81">
-        <v>262.991</v>
+        <v>266.32</v>
       </c>
       <c r="G81">
         <v>34.2</v>
@@ -7929,37 +7929,37 @@
         <v>28.25</v>
       </c>
       <c r="M81">
-        <v>52.8085928</v>
+        <v>53.477056</v>
       </c>
       <c r="N81">
-        <v>-24.5585928</v>
+        <v>-25.227056</v>
       </c>
       <c r="O81">
-        <v>-6.630820056</v>
+        <v>-6.81130512</v>
       </c>
       <c r="P81">
-        <v>-17.927772744</v>
+        <v>-18.41575088</v>
       </c>
       <c r="Q81">
-        <v>-17.927772744</v>
+        <v>-18.41575088</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2708662608308272</v>
+        <v>0.2821195738723685</v>
       </c>
       <c r="T81">
-        <v>4.12216760712265</v>
+        <v>4.328275987478782</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1444367212905548</v>
+        <v>0.1426312622744229</v>
       </c>
       <c r="W81">
-        <v>0.1717971063648566</v>
+        <v>0.1721596425352959</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5349508195946475</v>
+        <v>0.5282639343497144</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1941516288027104</v>
+        <v>0.1957016288027104</v>
       </c>
       <c r="C82">
-        <v>-135.3659427705192</v>
+        <v>-139.6953907970251</v>
       </c>
       <c r="D82">
-        <v>96.75405722948085</v>
+        <v>95.75360920297494</v>
       </c>
       <c r="E82">
-        <v>118.02</v>
+        <v>121.349</v>
       </c>
       <c r="F82">
-        <v>266.32</v>
+        <v>269.649</v>
       </c>
       <c r="G82">
         <v>34.2</v>
@@ -8011,37 +8011,37 @@
         <v>28.25</v>
       </c>
       <c r="M82">
-        <v>53.477056</v>
+        <v>54.1455192</v>
       </c>
       <c r="N82">
-        <v>-25.227056</v>
+        <v>-25.8955192</v>
       </c>
       <c r="O82">
-        <v>-6.81130512</v>
+        <v>-6.991790184000001</v>
       </c>
       <c r="P82">
-        <v>-18.41575088</v>
+        <v>-18.903729016</v>
       </c>
       <c r="Q82">
-        <v>-18.41575088</v>
+        <v>-18.903729016</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2821195738723685</v>
+        <v>0.2945574461814405</v>
       </c>
       <c r="T82">
-        <v>4.328275987478782</v>
+        <v>4.556079986819771</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1426312622744229</v>
+        <v>0.1408703824932572</v>
       </c>
       <c r="W82">
-        <v>0.1721596425352959</v>
+        <v>0.172513227195354</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5282639343497144</v>
+        <v>0.5217421573824339</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1957016288027104</v>
+        <v>0.1972516288027104</v>
       </c>
       <c r="C83">
-        <v>-139.6953907970251</v>
+        <v>-144.0043610716132</v>
       </c>
       <c r="D83">
-        <v>95.75360920297494</v>
+        <v>94.77363892838682</v>
       </c>
       <c r="E83">
-        <v>121.349</v>
+        <v>124.678</v>
       </c>
       <c r="F83">
-        <v>269.649</v>
+        <v>272.978</v>
       </c>
       <c r="G83">
         <v>34.2</v>
@@ -8093,37 +8093,37 @@
         <v>28.25</v>
       </c>
       <c r="M83">
-        <v>54.1455192</v>
+        <v>54.8139824</v>
       </c>
       <c r="N83">
-        <v>-25.8955192</v>
+        <v>-26.5639824</v>
       </c>
       <c r="O83">
-        <v>-6.991790184000001</v>
+        <v>-7.172275248000001</v>
       </c>
       <c r="P83">
-        <v>-18.903729016</v>
+        <v>-19.391707152</v>
       </c>
       <c r="Q83">
-        <v>-18.903729016</v>
+        <v>-19.391707152</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2945574461814405</v>
+        <v>0.3083773043026317</v>
       </c>
       <c r="T83">
-        <v>4.556079986819771</v>
+        <v>4.809195541643091</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1408703824932572</v>
+        <v>0.139152450999437</v>
       </c>
       <c r="W83">
-        <v>0.172513227195354</v>
+        <v>0.1728581878393131</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5217421573824339</v>
+        <v>0.5153794481460627</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1972516288027104</v>
+        <v>0.1988016288027104</v>
       </c>
       <c r="C84">
-        <v>-144.0043610716132</v>
+        <v>-148.2934759507065</v>
       </c>
       <c r="D84">
-        <v>94.77363892838682</v>
+        <v>93.81352404929348</v>
       </c>
       <c r="E84">
-        <v>124.678</v>
+        <v>128.007</v>
       </c>
       <c r="F84">
-        <v>272.978</v>
+        <v>276.307</v>
       </c>
       <c r="G84">
         <v>34.2</v>
@@ -8175,37 +8175,37 @@
         <v>28.25</v>
       </c>
       <c r="M84">
-        <v>54.8139824</v>
+        <v>55.48244560000001</v>
       </c>
       <c r="N84">
-        <v>-26.5639824</v>
+        <v>-27.23244560000001</v>
       </c>
       <c r="O84">
-        <v>-7.172275248000001</v>
+        <v>-7.352760312000002</v>
       </c>
       <c r="P84">
-        <v>-19.391707152</v>
+        <v>-19.879685288</v>
       </c>
       <c r="Q84">
-        <v>-19.391707152</v>
+        <v>-19.879685288</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3083773043026317</v>
+        <v>0.3238230280851395</v>
       </c>
       <c r="T84">
-        <v>4.809195541643091</v>
+        <v>5.092089397033862</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.139152450999437</v>
+        <v>0.1374759154452269</v>
       </c>
       <c r="W84">
-        <v>0.1728581878393131</v>
+        <v>0.1731948361785985</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5153794481460627</v>
+        <v>0.5091700572045439</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1988016288027104</v>
+        <v>0.2003516288027104</v>
       </c>
       <c r="C85">
-        <v>-148.2934759507065</v>
+        <v>-152.5633328242503</v>
       </c>
       <c r="D85">
-        <v>93.81352404929348</v>
+        <v>92.87266717574977</v>
       </c>
       <c r="E85">
-        <v>128.007</v>
+        <v>131.336</v>
       </c>
       <c r="F85">
-        <v>276.307</v>
+        <v>279.636</v>
       </c>
       <c r="G85">
         <v>34.2</v>
@@ -8257,37 +8257,37 @@
         <v>28.25</v>
       </c>
       <c r="M85">
-        <v>55.48244560000001</v>
+        <v>56.1509088</v>
       </c>
       <c r="N85">
-        <v>-27.23244560000001</v>
+        <v>-27.9009088</v>
       </c>
       <c r="O85">
-        <v>-7.352760312000002</v>
+        <v>-7.533245376000002</v>
       </c>
       <c r="P85">
-        <v>-19.879685288</v>
+        <v>-20.367663424</v>
       </c>
       <c r="Q85">
-        <v>-19.879685288</v>
+        <v>-20.367663424</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3238230280851395</v>
+        <v>0.3411994673404607</v>
       </c>
       <c r="T85">
-        <v>5.092089397033862</v>
+        <v>5.410344984348479</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1374759154452269</v>
+        <v>0.1358392974042123</v>
       </c>
       <c r="W85">
-        <v>0.1731948361785985</v>
+        <v>0.1735234690812342</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5091700572045439</v>
+        <v>0.5031085089044899</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2003516288027104</v>
+        <v>0.232555229174791</v>
       </c>
       <c r="C86">
-        <v>-152.5633328242502</v>
+        <v>-171.9070611530504</v>
       </c>
       <c r="D86">
-        <v>92.87266717574977</v>
+        <v>76.85793884694959</v>
       </c>
       <c r="E86">
-        <v>131.336</v>
+        <v>134.665</v>
       </c>
       <c r="F86">
-        <v>279.636</v>
+        <v>282.965</v>
       </c>
       <c r="G86">
         <v>34.2</v>
@@ -8339,45 +8339,45 @@
         <v>28.25</v>
       </c>
       <c r="M86">
-        <v>56.1509088</v>
+        <v>66.723147</v>
       </c>
       <c r="N86">
-        <v>-27.9009088</v>
+        <v>-38.473147</v>
       </c>
       <c r="O86">
-        <v>-7.533245375999999</v>
+        <v>-10.38774969</v>
       </c>
       <c r="P86">
-        <v>-20.367663424</v>
+        <v>-28.08539731</v>
       </c>
       <c r="Q86">
-        <v>-20.367663424</v>
+        <v>-28.08539731</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3411994673404605</v>
+        <v>0.3669167676436955</v>
       </c>
       <c r="T86">
-        <v>5.410344984348476</v>
+        <v>5.881366370945042</v>
       </c>
       <c r="U86">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1358392974042123</v>
+        <v>0.1143156512087177</v>
       </c>
       <c r="W86">
-        <v>0.1735234690812342</v>
+        <v>0.2088443694449844</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.50310850890449</v>
+        <v>0.4233913007730286</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.232555229174791</v>
+        <v>0.2344552291747911</v>
       </c>
       <c r="C87">
-        <v>-171.9070611530504</v>
+        <v>-176.0101191234972</v>
       </c>
       <c r="D87">
-        <v>76.85793884694959</v>
+        <v>76.08388087650282</v>
       </c>
       <c r="E87">
-        <v>134.665</v>
+        <v>137.994</v>
       </c>
       <c r="F87">
-        <v>282.965</v>
+        <v>286.294</v>
       </c>
       <c r="G87">
         <v>34.2</v>
@@ -8421,37 +8421,37 @@
         <v>28.25</v>
       </c>
       <c r="M87">
-        <v>66.723147</v>
+        <v>67.50812519999999</v>
       </c>
       <c r="N87">
-        <v>-38.473147</v>
+        <v>-39.25812519999999</v>
       </c>
       <c r="O87">
-        <v>-10.38774969</v>
+        <v>-10.599693804</v>
       </c>
       <c r="P87">
-        <v>-28.08539731</v>
+        <v>-28.658431396</v>
       </c>
       <c r="Q87">
-        <v>-28.08539731</v>
+        <v>-28.658431396</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3669167676436955</v>
+        <v>0.3898536796182452</v>
       </c>
       <c r="T87">
-        <v>5.881366370945042</v>
+        <v>6.301463968869689</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1143156512087177</v>
+        <v>0.1129863994504768</v>
       </c>
       <c r="W87">
-        <v>0.2088443694449844</v>
+        <v>0.2091578070095776</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4233913007730286</v>
+        <v>0.4184681461128771</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2344552291747911</v>
+        <v>0.2363552291747911</v>
       </c>
       <c r="C88">
-        <v>-176.0101191234972</v>
+        <v>-180.0977410426719</v>
       </c>
       <c r="D88">
-        <v>76.08388087650282</v>
+        <v>75.3252589573281</v>
       </c>
       <c r="E88">
-        <v>137.994</v>
+        <v>141.323</v>
       </c>
       <c r="F88">
-        <v>286.294</v>
+        <v>289.623</v>
       </c>
       <c r="G88">
         <v>34.2</v>
@@ -8503,37 +8503,37 @@
         <v>28.25</v>
       </c>
       <c r="M88">
-        <v>67.50812519999999</v>
+        <v>68.29310340000001</v>
       </c>
       <c r="N88">
-        <v>-39.25812519999999</v>
+        <v>-40.04310340000001</v>
       </c>
       <c r="O88">
-        <v>-10.599693804</v>
+        <v>-10.811637918</v>
       </c>
       <c r="P88">
-        <v>-28.658431396</v>
+        <v>-29.231465482</v>
       </c>
       <c r="Q88">
-        <v>-28.658431396</v>
+        <v>-29.231465482</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3898536796182452</v>
+        <v>0.4163193472811871</v>
       </c>
       <c r="T88">
-        <v>6.301463968869689</v>
+        <v>6.78619196647505</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1129863994504768</v>
+        <v>0.1116877052039196</v>
       </c>
       <c r="W88">
-        <v>0.2091578070095776</v>
+        <v>0.2094640391129158</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4184681461128771</v>
+        <v>0.4136581674219244</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2363552291747911</v>
+        <v>0.238255229174791</v>
       </c>
       <c r="C89">
-        <v>-180.0977410426719</v>
+        <v>-184.1703840843942</v>
       </c>
       <c r="D89">
-        <v>75.3252589573281</v>
+        <v>74.58161591560574</v>
       </c>
       <c r="E89">
-        <v>141.323</v>
+        <v>144.652</v>
       </c>
       <c r="F89">
-        <v>289.623</v>
+        <v>292.952</v>
       </c>
       <c r="G89">
         <v>34.2</v>
@@ -8585,37 +8585,37 @@
         <v>28.25</v>
       </c>
       <c r="M89">
-        <v>68.29310340000001</v>
+        <v>69.0780816</v>
       </c>
       <c r="N89">
-        <v>-40.04310340000001</v>
+        <v>-40.8280816</v>
       </c>
       <c r="O89">
-        <v>-10.811637918</v>
+        <v>-11.023582032</v>
       </c>
       <c r="P89">
-        <v>-29.231465482</v>
+        <v>-29.804499568</v>
       </c>
       <c r="Q89">
-        <v>-29.231465482</v>
+        <v>-29.804499568</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4163193472811871</v>
+        <v>0.4471959595546194</v>
       </c>
       <c r="T89">
-        <v>6.78619196647505</v>
+        <v>7.351707963681305</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1116877052039196</v>
+        <v>0.1104185267356932</v>
       </c>
       <c r="W89">
-        <v>0.2094640391129158</v>
+        <v>0.2097633113957235</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4136581674219244</v>
+        <v>0.4089575064284935</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.238255229174791</v>
+        <v>0.240155229174791</v>
       </c>
       <c r="C90">
-        <v>-184.1703840843942</v>
+        <v>-188.2284875453164</v>
       </c>
       <c r="D90">
-        <v>74.58161591560574</v>
+        <v>73.85251245468361</v>
       </c>
       <c r="E90">
-        <v>144.652</v>
+        <v>147.981</v>
       </c>
       <c r="F90">
-        <v>292.952</v>
+        <v>296.281</v>
       </c>
       <c r="G90">
         <v>34.2</v>
@@ -8667,37 +8667,37 @@
         <v>28.25</v>
       </c>
       <c r="M90">
-        <v>69.0780816</v>
+        <v>69.8630598</v>
       </c>
       <c r="N90">
-        <v>-40.8280816</v>
+        <v>-41.6130598</v>
       </c>
       <c r="O90">
-        <v>-11.023582032</v>
+        <v>-11.235526146</v>
       </c>
       <c r="P90">
-        <v>-29.804499568</v>
+        <v>-30.377533654</v>
       </c>
       <c r="Q90">
-        <v>-29.804499568</v>
+        <v>-30.377533654</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4471959595546194</v>
+        <v>0.4836865013323121</v>
       </c>
       <c r="T90">
-        <v>7.351707963681305</v>
+        <v>8.020045051288696</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1104185267356932</v>
+        <v>0.1091778691319214</v>
       </c>
       <c r="W90">
-        <v>0.2097633113957235</v>
+        <v>0.2100558584586929</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4089575064284935</v>
+        <v>0.4043624782663756</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.240155229174791</v>
+        <v>0.2420552291747911</v>
       </c>
       <c r="C91">
-        <v>-188.2284875453164</v>
+        <v>-192.272473710291</v>
       </c>
       <c r="D91">
-        <v>73.85251245468361</v>
+        <v>73.13752628970897</v>
       </c>
       <c r="E91">
-        <v>147.981</v>
+        <v>151.31</v>
       </c>
       <c r="F91">
-        <v>296.281</v>
+        <v>299.61</v>
       </c>
       <c r="G91">
         <v>34.2</v>
@@ -8749,37 +8749,37 @@
         <v>28.25</v>
       </c>
       <c r="M91">
-        <v>69.8630598</v>
+        <v>70.648038</v>
       </c>
       <c r="N91">
-        <v>-41.6130598</v>
+        <v>-42.398038</v>
       </c>
       <c r="O91">
-        <v>-11.235526146</v>
+        <v>-11.44747026</v>
       </c>
       <c r="P91">
-        <v>-30.377533654</v>
+        <v>-30.95056774</v>
       </c>
       <c r="Q91">
-        <v>-30.377533654</v>
+        <v>-30.95056774</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4836865013323121</v>
+        <v>0.5274751514655434</v>
       </c>
       <c r="T91">
-        <v>8.020045051288696</v>
+        <v>8.822049556417566</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1091778691319214</v>
+        <v>0.1079647816971223</v>
       </c>
       <c r="W91">
-        <v>0.2100558584586929</v>
+        <v>0.2103419044758186</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4043624782663756</v>
+        <v>0.3998695618411937</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2420552291747911</v>
+        <v>0.2439552291747911</v>
       </c>
       <c r="C92">
-        <v>-192.272473710291</v>
+        <v>-196.302748667955</v>
       </c>
       <c r="D92">
-        <v>73.13752628970897</v>
+        <v>72.436251332045</v>
       </c>
       <c r="E92">
-        <v>151.31</v>
+        <v>154.639</v>
       </c>
       <c r="F92">
-        <v>299.61</v>
+        <v>302.939</v>
       </c>
       <c r="G92">
         <v>34.2</v>
@@ -8831,37 +8831,37 @@
         <v>28.25</v>
       </c>
       <c r="M92">
-        <v>70.648038</v>
+        <v>71.4330162</v>
       </c>
       <c r="N92">
-        <v>-42.398038</v>
+        <v>-43.1830162</v>
       </c>
       <c r="O92">
-        <v>-11.44747026</v>
+        <v>-11.659414374</v>
       </c>
       <c r="P92">
-        <v>-30.95056774</v>
+        <v>-31.523601826</v>
       </c>
       <c r="Q92">
-        <v>-30.95056774</v>
+        <v>-31.523601826</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5274751514655434</v>
+        <v>0.5809946127394926</v>
       </c>
       <c r="T92">
-        <v>8.822049556417566</v>
+        <v>9.802277284908408</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1079647816971223</v>
+        <v>0.1067783555246264</v>
       </c>
       <c r="W92">
-        <v>0.2103419044758186</v>
+        <v>0.2106216637672931</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3998695618411937</v>
+        <v>0.3954753908319498</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2439552291747911</v>
+        <v>0.245855229174791</v>
       </c>
       <c r="C93">
-        <v>-196.302748667955</v>
+        <v>-200.3197030798371</v>
       </c>
       <c r="D93">
-        <v>72.436251332045</v>
+        <v>71.7482969201629</v>
       </c>
       <c r="E93">
-        <v>154.639</v>
+        <v>157.968</v>
       </c>
       <c r="F93">
-        <v>302.939</v>
+        <v>306.268</v>
       </c>
       <c r="G93">
         <v>34.2</v>
@@ -8913,37 +8913,37 @@
         <v>28.25</v>
       </c>
       <c r="M93">
-        <v>71.4330162</v>
+        <v>72.21799439999999</v>
       </c>
       <c r="N93">
-        <v>-43.1830162</v>
+        <v>-43.96799439999999</v>
       </c>
       <c r="O93">
-        <v>-11.659414374</v>
+        <v>-11.871358488</v>
       </c>
       <c r="P93">
-        <v>-31.523601826</v>
+        <v>-32.096635912</v>
       </c>
       <c r="Q93">
-        <v>-31.523601826</v>
+        <v>-32.096635912</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5809946127394926</v>
+        <v>0.6478939393319294</v>
       </c>
       <c r="T93">
-        <v>9.802277284908408</v>
+        <v>11.02756194552196</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1067783555246264</v>
+        <v>0.1056177212254457</v>
       </c>
       <c r="W93">
-        <v>0.2106216637672931</v>
+        <v>0.2108953413350399</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3954753908319498</v>
+        <v>0.3911767452794286</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.245855229174791</v>
+        <v>0.247755229174791</v>
       </c>
       <c r="C94">
-        <v>-200.3197030798371</v>
+        <v>-204.3237129060512</v>
       </c>
       <c r="D94">
-        <v>71.7482969201629</v>
+        <v>71.07328709394878</v>
       </c>
       <c r="E94">
-        <v>157.968</v>
+        <v>161.297</v>
       </c>
       <c r="F94">
-        <v>306.268</v>
+        <v>309.597</v>
       </c>
       <c r="G94">
         <v>34.2</v>
@@ -8995,37 +8995,37 @@
         <v>28.25</v>
       </c>
       <c r="M94">
-        <v>72.21799439999999</v>
+        <v>73.00297259999999</v>
       </c>
       <c r="N94">
-        <v>-43.96799439999999</v>
+        <v>-44.75297259999999</v>
       </c>
       <c r="O94">
-        <v>-11.871358488</v>
+        <v>-12.083302602</v>
       </c>
       <c r="P94">
-        <v>-32.096635912</v>
+        <v>-32.669669998</v>
       </c>
       <c r="Q94">
-        <v>-32.096635912</v>
+        <v>-32.669669998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6478939393319294</v>
+        <v>0.7339073592364908</v>
       </c>
       <c r="T94">
-        <v>11.02756194552196</v>
+        <v>12.60292793773939</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1056177212254457</v>
+        <v>0.1044820468036668</v>
       </c>
       <c r="W94">
-        <v>0.2108953413350399</v>
+        <v>0.2111631333636954</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3911767452794286</v>
+        <v>0.3869705437172842</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.247755229174791</v>
+        <v>0.249655229174791</v>
       </c>
       <c r="C95">
-        <v>-204.3237129060512</v>
+        <v>-208.3151400904072</v>
       </c>
       <c r="D95">
-        <v>71.07328709394878</v>
+        <v>70.41085990959276</v>
       </c>
       <c r="E95">
-        <v>161.297</v>
+        <v>164.626</v>
       </c>
       <c r="F95">
-        <v>309.597</v>
+        <v>312.926</v>
       </c>
       <c r="G95">
         <v>34.2</v>
@@ -9077,37 +9077,37 @@
         <v>28.25</v>
       </c>
       <c r="M95">
-        <v>73.00297259999999</v>
+        <v>73.7879508</v>
       </c>
       <c r="N95">
-        <v>-44.75297259999999</v>
+        <v>-45.5379508</v>
       </c>
       <c r="O95">
-        <v>-12.083302602</v>
+        <v>-12.295246716</v>
       </c>
       <c r="P95">
-        <v>-32.669669998</v>
+        <v>-33.242704084</v>
       </c>
       <c r="Q95">
-        <v>-32.669669998</v>
+        <v>-33.242704084</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7339073592364908</v>
+        <v>0.8485919191092395</v>
       </c>
       <c r="T95">
-        <v>12.60292793773939</v>
+        <v>14.70341592736262</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1044820468036668</v>
+        <v>0.1033705356674575</v>
       </c>
       <c r="W95">
-        <v>0.2111631333636954</v>
+        <v>0.2114252276896135</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3869705437172842</v>
+        <v>0.3828538358053981</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.249655229174791</v>
+        <v>0.2515552291747911</v>
       </c>
       <c r="C96">
-        <v>-208.3151400904072</v>
+        <v>-212.2943332075628</v>
       </c>
       <c r="D96">
-        <v>70.41085990959276</v>
+        <v>69.76066679243716</v>
       </c>
       <c r="E96">
-        <v>164.626</v>
+        <v>167.955</v>
       </c>
       <c r="F96">
-        <v>312.926</v>
+        <v>316.255</v>
       </c>
       <c r="G96">
         <v>34.2</v>
@@ -9159,37 +9159,37 @@
         <v>28.25</v>
       </c>
       <c r="M96">
-        <v>73.7879508</v>
+        <v>74.572929</v>
       </c>
       <c r="N96">
-        <v>-45.5379508</v>
+        <v>-46.322929</v>
       </c>
       <c r="O96">
-        <v>-12.295246716</v>
+        <v>-12.50719083</v>
       </c>
       <c r="P96">
-        <v>-33.242704084</v>
+        <v>-33.81573817</v>
       </c>
       <c r="Q96">
-        <v>-33.242704084</v>
+        <v>-33.81573817</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8485919191092395</v>
+        <v>1.009150302931088</v>
       </c>
       <c r="T96">
-        <v>14.70341592736262</v>
+        <v>17.64409911283515</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1033705356674575</v>
+        <v>0.1022824247656948</v>
       </c>
       <c r="W96">
-        <v>0.2114252276896135</v>
+        <v>0.2116818042402492</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3828538358053981</v>
+        <v>0.3788237954284992</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2515552291747911</v>
+        <v>0.2534552291747911</v>
       </c>
       <c r="C97">
-        <v>-212.2943332075628</v>
+        <v>-216.2616280746479</v>
       </c>
       <c r="D97">
-        <v>69.76066679243716</v>
+        <v>69.12237192535214</v>
       </c>
       <c r="E97">
-        <v>167.955</v>
+        <v>171.284</v>
       </c>
       <c r="F97">
-        <v>316.255</v>
+        <v>319.584</v>
       </c>
       <c r="G97">
         <v>34.2</v>
@@ -9241,37 +9241,37 @@
         <v>28.25</v>
       </c>
       <c r="M97">
-        <v>74.572929</v>
+        <v>75.3579072</v>
       </c>
       <c r="N97">
-        <v>-46.322929</v>
+        <v>-47.1079072</v>
       </c>
       <c r="O97">
-        <v>-12.50719083</v>
+        <v>-12.719134944</v>
       </c>
       <c r="P97">
-        <v>-33.81573817</v>
+        <v>-34.388772256</v>
       </c>
       <c r="Q97">
-        <v>-33.81573817</v>
+        <v>-34.388772256</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.009150302931088</v>
+        <v>1.249987878663861</v>
       </c>
       <c r="T97">
-        <v>17.64409911283515</v>
+        <v>22.05512389104395</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1022824247656948</v>
+        <v>0.1012169828410521</v>
       </c>
       <c r="W97">
-        <v>0.2116818042402492</v>
+        <v>0.2119330354460799</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3788237954284992</v>
+        <v>0.374877714226119</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.253455229174791</v>
+        <v>0.255355229174791</v>
       </c>
       <c r="C98">
-        <v>-216.2616280746478</v>
+        <v>-220.2173483296152</v>
       </c>
       <c r="D98">
-        <v>69.12237192535214</v>
+        <v>68.4956516703848</v>
       </c>
       <c r="E98">
-        <v>171.2839999999999</v>
+        <v>174.6129999999999</v>
       </c>
       <c r="F98">
-        <v>319.5839999999999</v>
+        <v>322.913</v>
       </c>
       <c r="G98">
         <v>34.2</v>
@@ -9323,37 +9323,37 @@
         <v>28.25</v>
       </c>
       <c r="M98">
-        <v>75.35790719999999</v>
+        <v>76.1428854</v>
       </c>
       <c r="N98">
-        <v>-47.10790719999999</v>
+        <v>-47.8928854</v>
       </c>
       <c r="O98">
-        <v>-12.719134944</v>
+        <v>-12.931079058</v>
       </c>
       <c r="P98">
-        <v>-34.38877225599999</v>
+        <v>-34.961806342</v>
       </c>
       <c r="Q98">
-        <v>-34.38877225599999</v>
+        <v>-34.961806342</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.249987878663857</v>
+        <v>1.651383838218476</v>
       </c>
       <c r="T98">
-        <v>22.05512389104389</v>
+        <v>29.40683185472519</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1012169828410522</v>
+        <v>0.1001735087911444</v>
       </c>
       <c r="W98">
-        <v>0.2119330354460799</v>
+        <v>0.2121790866270482</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3748777142261192</v>
+        <v>0.371012995522757</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.255355229174791</v>
+        <v>0.257255229174791</v>
       </c>
       <c r="C99">
-        <v>-220.2173483296152</v>
+        <v>-224.1618059784121</v>
       </c>
       <c r="D99">
-        <v>68.4956516703848</v>
+        <v>67.88019402158785</v>
       </c>
       <c r="E99">
-        <v>174.6129999999999</v>
+        <v>177.942</v>
       </c>
       <c r="F99">
-        <v>322.913</v>
+        <v>326.242</v>
       </c>
       <c r="G99">
         <v>34.2</v>
@@ -9405,37 +9405,37 @@
         <v>28.25</v>
       </c>
       <c r="M99">
-        <v>76.1428854</v>
+        <v>76.92786359999999</v>
       </c>
       <c r="N99">
-        <v>-47.8928854</v>
+        <v>-48.67786359999999</v>
       </c>
       <c r="O99">
-        <v>-12.931079058</v>
+        <v>-13.143023172</v>
       </c>
       <c r="P99">
-        <v>-34.961806342</v>
+        <v>-35.534840428</v>
       </c>
       <c r="Q99">
-        <v>-34.961806342</v>
+        <v>-35.534840428</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.651383838218476</v>
+        <v>2.454175757327714</v>
       </c>
       <c r="T99">
-        <v>29.40683185472519</v>
+        <v>44.11024778208778</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1001735087911444</v>
+        <v>0.09915133013001028</v>
       </c>
       <c r="W99">
-        <v>0.2121790866270482</v>
+        <v>0.2124201163553436</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.371012995522757</v>
+        <v>0.3672271486296677</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.257255229174791</v>
+        <v>0.259155229174791</v>
       </c>
       <c r="C100">
-        <v>-224.1618059784121</v>
+        <v>-228.0953019129146</v>
       </c>
       <c r="D100">
-        <v>67.88019402158785</v>
+        <v>67.27569808708535</v>
       </c>
       <c r="E100">
-        <v>177.942</v>
+        <v>181.271</v>
       </c>
       <c r="F100">
-        <v>326.242</v>
+        <v>329.571</v>
       </c>
       <c r="G100">
         <v>34.2</v>
@@ -9487,37 +9487,37 @@
         <v>28.25</v>
       </c>
       <c r="M100">
-        <v>76.92786359999999</v>
+        <v>77.71284179999999</v>
       </c>
       <c r="N100">
-        <v>-48.67786359999999</v>
+        <v>-49.46284179999999</v>
       </c>
       <c r="O100">
-        <v>-13.143023172</v>
+        <v>-13.354967286</v>
       </c>
       <c r="P100">
-        <v>-35.534840428</v>
+        <v>-36.107874514</v>
       </c>
       <c r="Q100">
-        <v>-35.534840428</v>
+        <v>-36.107874514</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.454175757327714</v>
+        <v>4.862551514655428</v>
       </c>
       <c r="T100">
-        <v>44.11024778208778</v>
+        <v>88.22049556417556</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09915133013001028</v>
+        <v>0.09814980154283846</v>
       </c>
       <c r="W100">
-        <v>0.2124201163553436</v>
+        <v>0.2126562767961987</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3672271486296677</v>
+        <v>0.3635177834919943</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.259155229174791</v>
-      </c>
-      <c r="C101">
-        <v>-228.0953019129146</v>
-      </c>
-      <c r="D101">
-        <v>67.27569808708535</v>
-      </c>
-      <c r="E101">
-        <v>181.271</v>
-      </c>
-      <c r="F101">
-        <v>329.571</v>
-      </c>
-      <c r="G101">
-        <v>34.2</v>
-      </c>
-      <c r="H101">
-        <v>184.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>28.25</v>
-      </c>
-      <c r="K101">
-        <v>0</v>
-      </c>
-      <c r="L101">
-        <v>28.25</v>
-      </c>
-      <c r="M101">
-        <v>77.71284179999999</v>
-      </c>
-      <c r="N101">
-        <v>-49.46284179999999</v>
-      </c>
-      <c r="O101">
-        <v>-13.354967286</v>
-      </c>
-      <c r="P101">
-        <v>-36.107874514</v>
-      </c>
-      <c r="Q101">
-        <v>-36.107874514</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.862551514655428</v>
-      </c>
-      <c r="T101">
-        <v>88.22049556417556</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09814980154283846</v>
-      </c>
-      <c r="W101">
-        <v>0.2126562767961987</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3635177834919943</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
